--- a/data/france/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:BP12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,301 +480,381 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>ball_possession_home</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ball_possession_away</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>goal_attempts_home</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>goal_attempts_away</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>shots_on_goal_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>shots_on_goal_away</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>fouls_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>fouls_away</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>interceptions_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>interceptions_away</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>id_country</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>id_competition</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>is_cup</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>season</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>id_team_home_rival_team</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_home</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_away</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_home</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_away</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OA5YizjL</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45523.65625</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">thual o 
+          <t xml:space="preserve">kherradji a 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>67394</v>
+        <v>50186</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ADl76OZP</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>jgNAYRGi</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="K2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M2" t="n">
+        <v>67</v>
+      </c>
+      <c r="N2" t="n">
         <v>33</v>
       </c>
-      <c r="L2" t="n">
-        <v>67</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N2" t="n">
-        <v>18</v>
-      </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T2" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>EwpPg8iH</t>
+          <t>nVS1TlC4</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Cp0gM1r4</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>55</v>
       </c>
       <c r="X2" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -783,146 +863,216 @@
         <v>20242025</v>
       </c>
       <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
+      <c r="AE2" t="n">
+        <v>22.625</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>74.5</v>
+      </c>
       <c r="AI2" t="n">
-        <v>24.44444444444444</v>
+        <v>11625000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>178.1111111111111</v>
+        <v>81.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
+        <v>25.1</v>
       </c>
       <c r="AL2" t="n">
-        <v>71.77777777777777</v>
+        <v>185.4</v>
       </c>
       <c r="AM2" t="n">
-        <v>4622222.222222222</v>
+        <v>1</v>
       </c>
       <c r="AN2" t="n">
-        <v>77.11111111111111</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
+        <v>67.3</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1507500</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>73</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>25.07142857142857</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>179.3571428571429</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.357142857142857</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>73</v>
+      </c>
       <c r="AU2" t="n">
-        <v>21.73333333333333</v>
+        <v>6525000</v>
       </c>
       <c r="AV2" t="n">
-        <v>177.4</v>
+        <v>78.64285714285714</v>
       </c>
       <c r="AW2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AX2" t="n">
-        <v>69.06666666666666</v>
+        <v>181.1739130434783</v>
       </c>
       <c r="AY2" t="n">
-        <v>2781666.666666667</v>
+        <v>1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>77.53333333333333</v>
+        <v>66.34782608695652</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1292391.304347826</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>71.95652173913044</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>178</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>461</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>66800000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>471</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>23</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>176</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>131</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>2325000</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>144</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>lEQmcVR0</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45523.65625</v>
+        <v>45528.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">petit a 
+          <t xml:space="preserve">frappart s 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade saint symphorien
-  metz </t>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>28786</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>59186</v>
+      </c>
+      <c r="F3" t="n">
+        <v>54392</v>
+      </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4v0yqlWc</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>AZwK8L6R</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>67</v>
+        <v>0.44</v>
       </c>
       <c r="L3" t="n">
-        <v>33</v>
+        <v>2.82</v>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N3" t="n">
+        <v>68</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="O3" t="n">
-        <v>5</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>13</v>
-      </c>
-      <c r="R3" t="n">
-        <v>15</v>
-      </c>
-      <c r="S3" t="n">
-        <v>12</v>
-      </c>
-      <c r="T3" t="n">
-        <v>6</v>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>h89kUbu5</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>fo8nHfg4</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="W3" t="n">
         <v>55</v>
       </c>
       <c r="X3" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -930,84 +1080,1738 @@
       <c r="Z3" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>179.7777777777778</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>10300000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>79.77777777777777</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>11600000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>24.95652173913043</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>180.7391304347826</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.739130434782609</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>74.39130434782609</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7004347.826086956</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>79.47826086956522</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>21.16666666666667</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>183.1666666666667</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>73.72222222222223</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>11236111.11111111</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>82</v>
+      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="n">
+        <v>18</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>173</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>66</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45527.65625</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>71</v>
+      </c>
+      <c r="N4" t="n">
+        <v>29</v>
+      </c>
+      <c r="O4" t="n">
+        <v>21</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>10</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T4" t="n">
+        <v>16</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>55</v>
+      </c>
+      <c r="X4" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="n">
+        <v>26.45454545454545</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>180.2727272727273</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>73.90909090909091</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>5527272.727272728</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>77.27272727272727</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>184</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.866666666666667</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>77.93333333333334</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>27520000</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>84.33333333333333</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>25.08333333333333</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5383333.333333333</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>76.33333333333333</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>27.71428571428572</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>183.7142857142857</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2.571428571428572</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>563</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>162500000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>568</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>196</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>74</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>2yXIHV57</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45528.39583333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">benchabane f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade du moustoir
+  lorient </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>16787</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>52</v>
+      </c>
+      <c r="N5" t="n">
+        <v>48</v>
+      </c>
+      <c r="O5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P5" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>12</v>
+      </c>
+      <c r="T5" t="n">
+        <v>10</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>55</v>
+      </c>
+      <c r="X5" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
+        <v>24.44444444444444</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>178.1111111111111</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>71.77777777777777</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>4622222.222222222</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>77.11111111111111</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>182.6363636363636</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>66.72727272727273</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1343181.818181818</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>20.92857142857143</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>178.5714285714286</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>68.28571428571429</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2466071.428571429</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>78.42857142857143</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>26.38461538461538</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>184.3076923076923</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.153846153846154</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>66.38461538461539</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1365384.615384615</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>71.69230769230769</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>GM5aU8kD</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45527.625</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des sports
+  annecy </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>15660</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>59</v>
+      </c>
+      <c r="N6" t="n">
+        <v>41</v>
+      </c>
+      <c r="O6" t="n">
+        <v>25</v>
+      </c>
+      <c r="P6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>7</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>13</v>
+      </c>
+      <c r="T6" t="n">
+        <v>13</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>55</v>
+      </c>
+      <c r="X6" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>182</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>64.44444444444444</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>841666.6666666666</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>68.11111111111111</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>181.2727272727273</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>64.36363636363636</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>881818.1818181818</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>70.36363636363636</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>r97iWUK0</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45527.625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lesage m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade armand cesari
+  bastia </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>16048</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>59</v>
+      </c>
+      <c r="N7" t="n">
+        <v>41</v>
+      </c>
+      <c r="O7" t="n">
+        <v>15</v>
+      </c>
+      <c r="P7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>12</v>
+      </c>
+      <c r="T7" t="n">
+        <v>11</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>55</v>
+      </c>
+      <c r="X7" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1205000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>180.8571428571429</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>63.78571428571428</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>832142.8571428572</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>67.57142857142857</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>181.0666666666667</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>728333.3333333334</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>71.53333333333333</v>
+      </c>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+      <c r="BO7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>MaSQpUZg</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45527.625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thual o 
+  fra </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le basser
+  laval </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>11017</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>47</v>
+      </c>
+      <c r="N8" t="n">
+        <v>53</v>
+      </c>
+      <c r="O8" t="n">
+        <v>16</v>
+      </c>
+      <c r="P8" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>23</v>
+      </c>
+      <c r="T8" t="n">
+        <v>16</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>55</v>
+      </c>
+      <c r="X8" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>181.125</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1281250</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>72.625</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>24.11111111111111</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>179.8888888888889</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>65.33333333333333</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1077777.777777778</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>70.44444444444444</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>177.75</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>64.58333333333333</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>832500</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>71</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>60.33333333333334</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>686111.1111111111</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>69.77777777777777</v>
+      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>WUmnhCsK</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45527.625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taleb a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la licorne
+  amiens </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>12097</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>66</v>
+      </c>
+      <c r="N9" t="n">
+        <v>34</v>
+      </c>
+      <c r="O9" t="n">
+        <v>9</v>
+      </c>
+      <c r="P9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>17</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>55</v>
+      </c>
+      <c r="X9" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="n">
+        <v>24.11111111111111</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>178.8888888888889</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>67.33333333333333</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1747222.222222222</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>26.17647058823529</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>177.1764705882353</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>66.17647058823529</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1182352.941176471</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>69.23529411764706</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>179.5833333333333</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>63.83333333333334</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>931250</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>72.91666666666667</v>
+      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>nsErYjjl</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45527.625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leleu m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nouste camp
+  pau </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4031</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>32</v>
+      </c>
+      <c r="N10" t="n">
+        <v>68</v>
+      </c>
+      <c r="O10" t="n">
+        <v>7</v>
+      </c>
+      <c r="P10" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>12</v>
+      </c>
+      <c r="T10" t="n">
+        <v>20</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>55</v>
+      </c>
+      <c r="X10" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>64.88888888888889</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1066666.666666667</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>73</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>26.375</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1643750</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>26.84615384615385</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>181.3076923076923</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>65.46153846153847</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>786538.4615384615</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>70.92307692307692</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>20.23076923076923</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>181.4615384615385</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>62.53846153846154</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>875000</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>75.38461538461539</v>
+      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UsP4uZcE</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45527.625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landry r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade paul lignon
+  rodez </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5955</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>38</v>
+      </c>
+      <c r="N11" t="n">
+        <v>62</v>
+      </c>
+      <c r="O11" t="n">
+        <v>16</v>
+      </c>
+      <c r="P11" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>14</v>
+      </c>
+      <c r="T11" t="n">
+        <v>13</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>55</v>
+      </c>
+      <c r="X11" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
         <is>
           <t>nP6UzIU1</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="n">
-        <v>24.90909090909091</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>177.8181818181818</v>
-      </c>
-      <c r="AE3" t="n">
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="n">
+        <v>26.81818181818182</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>176.8181818181818</v>
+      </c>
+      <c r="AM11" t="n">
         <v>1.090909090909091</v>
       </c>
-      <c r="AF3" t="n">
-        <v>68.90909090909091</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1677272.727272727</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>75.27272727272727</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>25.375</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>179.625</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>63.625</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>723125</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>68.375</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>181.0909090909091</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>67.81818181818181</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1718181.818181818</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>23.25</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>180</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>679166.6666666666</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>68.16666666666667</v>
-      </c>
+      <c r="AN11" t="n">
+        <v>70.54545454545455</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1861363.636363636</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>73.90909090909091</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>20.9375</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>62.3125</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>829687.5</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>72.4375</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>20.375</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>65.75</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1696875</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>77</v>
+      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+      <c r="BO11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>4rrRVcF7</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45527.625</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapapria r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l aube
+  troyes </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>20420</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>48</v>
+      </c>
+      <c r="N12" t="n">
+        <v>52</v>
+      </c>
+      <c r="O12" t="n">
+        <v>16</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>13</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>55</v>
+      </c>
+      <c r="X12" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="n">
+        <v>24.22222222222222</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>177.7777777777778</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>64.66666666666667</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1072222.222222222</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1553125</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>74</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>27.05882352941176</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>179.3529411764706</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.176470588235294</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>67.35294117647059</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1388235.294117647</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>70.70588235294117</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>178.625</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>65.625</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1637500</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>72.875</v>
+      </c>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+      <c r="BO12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI3"/>
+  <dimension ref="A1:BH9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,251 +570,244 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>id_team_home_rival_team</t>
+          <t>id_team_away_rival_team</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_start_home</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_start_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_home</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_away</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_home</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_home</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_miss_home</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_home</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_home</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>sum_val_player_miss_home</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hhlQ5IbD</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.65625</v>
+        <v>45534.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ben el hadj salem h 
+          <t xml:space="preserve">leonard t 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>67394</v>
-      </c>
-      <c r="F2" t="n">
-        <v>63841</v>
-      </c>
+        <v>59186</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.66</v>
+        <v>2.23</v>
       </c>
       <c r="L2" t="n">
-        <v>0.88</v>
+        <v>2.24</v>
       </c>
       <c r="M2" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="N2" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="P2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
       </c>
       <c r="T2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>pYizckpN</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -833,171 +826,178 @@
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>lhUkVMh2</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>27.22222222222222</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>183.2222222222222</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>76.55555555555556</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>9666666.666666666</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>78.77777777777777</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>23.8</v>
+        <v>20.9</v>
       </c>
       <c r="AK2" t="n">
-        <v>178</v>
+        <v>184.1</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>74.2</v>
+        <v>70</v>
       </c>
       <c r="AN2" t="n">
-        <v>11320000</v>
+        <v>4042500</v>
       </c>
       <c r="AO2" t="n">
-        <v>78.8</v>
+        <v>80.3</v>
       </c>
       <c r="AP2" t="n">
-        <v>21.2</v>
+        <v>23.15384615384615</v>
       </c>
       <c r="AQ2" t="n">
-        <v>183.9333333333333</v>
+        <v>181.0769230769231</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.066666666666667</v>
+        <v>1.307692307692308</v>
       </c>
       <c r="AS2" t="n">
-        <v>67.86666666666666</v>
+        <v>73.30769230769231</v>
       </c>
       <c r="AT2" t="n">
-        <v>3386666.666666667</v>
+        <v>6023076.923076923</v>
       </c>
       <c r="AU2" t="n">
-        <v>77.86666666666666</v>
+        <v>80.30769230769231</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>20.75</v>
       </c>
       <c r="AW2" t="n">
-        <v>182</v>
+        <v>182.1666666666667</v>
       </c>
       <c r="AX2" t="n">
         <v>1</v>
       </c>
       <c r="AY2" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>77.33333333333333</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>175</v>
+      </c>
+      <c r="BD2" t="n">
         <v>2</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>135</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5700000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>153</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>180</v>
-      </c>
       <c r="BE2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BF2" t="n">
-        <v>1</v>
+        <v>152</v>
       </c>
       <c r="BG2" t="n">
-        <v>74</v>
+        <v>22000000</v>
       </c>
       <c r="BH2" t="n">
-        <v>9500000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>82</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0pvInj5s</t>
+          <t>WlzDg17E</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45530.65625</v>
+        <v>45534.625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bouille t 
+          <t xml:space="preserve">petit a 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade bauer
-  paris   saint ouen </t>
+          <t xml:space="preserve">michel moretti stadium
+  ajaccio </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F3" t="n">
-        <v>4560</v>
-      </c>
+        <v>8470</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2kM6ufaS</t>
+          <t>2aeoANM8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2aeoANM8</t>
+          <t>fsfAHubD</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="N3" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="O3" t="n">
+        <v>23</v>
+      </c>
+      <c r="P3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q3" t="n">
         <v>5</v>
       </c>
-      <c r="P3" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2</v>
-      </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T3" t="n">
         <v>15</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SzfSpYcf</t>
+          <t>8tmnzqxe</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>8tmnzqxe</t>
+          <t>4vG8dmrf</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -1013,72 +1013,84 @@
         <v>20242025</v>
       </c>
       <c r="AA3" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AB3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>27.66666666666667</v>
+        <v>24.22222222222222</v>
       </c>
       <c r="AE3" t="n">
-        <v>176.4444444444445</v>
+        <v>182</v>
       </c>
       <c r="AF3" t="n">
         <v>1</v>
       </c>
       <c r="AG3" t="n">
-        <v>65.11111111111111</v>
+        <v>64.66666666666667</v>
       </c>
       <c r="AH3" t="n">
-        <v>722222.2222222222</v>
+        <v>1016666.666666667</v>
       </c>
       <c r="AI3" t="n">
-        <v>68.55555555555556</v>
+        <v>70.55555555555556</v>
       </c>
       <c r="AJ3" t="n">
-        <v>22.5</v>
+        <v>24.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>187</v>
+        <v>176.375</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>66</v>
+        <v>65.125</v>
       </c>
       <c r="AN3" t="n">
-        <v>1687500</v>
+        <v>1168750</v>
       </c>
       <c r="AO3" t="n">
-        <v>77</v>
+        <v>70.875</v>
       </c>
       <c r="AP3" t="n">
-        <v>24.52380952380953</v>
+        <v>28.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>182.4761904761905</v>
+        <v>176.1875</v>
       </c>
       <c r="AR3" t="n">
         <v>1</v>
       </c>
       <c r="AS3" t="n">
-        <v>65.76190476190476</v>
+        <v>65.8125</v>
       </c>
       <c r="AT3" t="n">
-        <v>1139285.714285714</v>
+        <v>715625</v>
       </c>
       <c r="AU3" t="n">
-        <v>71.57142857142857</v>
-      </c>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
+        <v>70.0625</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>27.6875</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>65.625</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1020312.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>68.5</v>
+      </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
@@ -1086,7 +1098,966 @@
       <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>IoCT4kRP</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45534.625</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">valnet a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade michel d ornano
+  caen </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>20300</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>77</v>
+      </c>
+      <c r="N4" t="n">
+        <v>23</v>
+      </c>
+      <c r="O4" t="n">
+        <v>12</v>
+      </c>
+      <c r="P4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T4" t="n">
+        <v>20</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>55</v>
+      </c>
+      <c r="X4" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>65.625</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1428125</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>74.625</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="n">
+        <v>26.72222222222222</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>183.8333333333333</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>67.94444444444444</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1638888.888888889</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>680000</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>zyWS0tQi</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45534.625</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kubler g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade gabriel montpied
+  clermont ferrand </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>37</v>
+      </c>
+      <c r="N5" t="n">
+        <v>63</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>12</v>
+      </c>
+      <c r="T5" t="n">
+        <v>9</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>55</v>
+      </c>
+      <c r="X5" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>181.875</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>68.125</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1715625</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>177.8888888888889</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>67.22222222222223</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1697222.222222222</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>71.55555555555556</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>176.125</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>64.375</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1425000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>72.625</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>26.64285714285714</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>177.7857142857143</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.071428571428571</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>67.21428571428571</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1314285.714285714</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>69.78571428571429</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>06FhaTlm</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45534.625</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rosier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade marcel tribut
+  dunkerque </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4933</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>52</v>
+      </c>
+      <c r="N6" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" t="n">
+        <v>13</v>
+      </c>
+      <c r="P6" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9</v>
+      </c>
+      <c r="T6" t="n">
+        <v>14</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>55</v>
+      </c>
+      <c r="X6" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="n">
+        <v>22.92307692307692</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>175.8461538461538</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>64.30769230769231</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1073076.923076923</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>73.23076923076923</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>21.30769230769231</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>184.0769230769231</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>62</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>726923.0769230769</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>71.30769230769231</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>UPVYr846</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45534.625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lesage m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade des alpes
+  grenoble </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>20068</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>49</v>
+      </c>
+      <c r="N7" t="n">
+        <v>51</v>
+      </c>
+      <c r="O7" t="n">
+        <v>7</v>
+      </c>
+      <c r="P7" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>11</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>55</v>
+      </c>
+      <c r="X7" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>185.7</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1597500</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>23.44444444444444</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>182.2222222222222</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>64.11111111111111</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>975000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>71.88888888888889</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>25.64285714285714</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>181</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>67.71428571428571</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1848214.285714286</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>73.42857142857143</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>27.88888888888889</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>177.6666666666667</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>65.33333333333333</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>736111.1111111111</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>69</v>
+      </c>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8WI0c7Ja</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45534.625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapapria r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de roudourou
+  guingamp </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>19060</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>62</v>
+      </c>
+      <c r="N8" t="n">
+        <v>38</v>
+      </c>
+      <c r="O8" t="n">
+        <v>21</v>
+      </c>
+      <c r="P8" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7</v>
+      </c>
+      <c r="S8" t="n">
+        <v>12</v>
+      </c>
+      <c r="T8" t="n">
+        <v>10</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>55</v>
+      </c>
+      <c r="X8" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="n">
+        <v>24.11111111111111</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>179.8888888888889</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>65.33333333333333</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1077777.777777778</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>70.44444444444444</v>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="n">
+        <v>22.92857142857143</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>180.4285714285714</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>61.57142857142857</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>760714.2857142857</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>QiPssnZI</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45534.625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landry r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>48</v>
+      </c>
+      <c r="N9" t="n">
+        <v>52</v>
+      </c>
+      <c r="O9" t="n">
+        <v>13</v>
+      </c>
+      <c r="P9" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>22</v>
+      </c>
+      <c r="T9" t="n">
+        <v>16</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>55</v>
+      </c>
+      <c r="X9" t="n">
+        <v>555</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>967500</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>67</v>
+      </c>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH9"/>
+  <dimension ref="A1:BP5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,244 +570,284 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>id_team_home_rival_team</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_home</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_away</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_home</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_away</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_home</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_home</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_miss_home</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_home</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_home</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>sum_val_player_miss_home</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vmgpBDzg</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45534.65625</v>
+        <v>45535.58333333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">millot b 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>59186</v>
+        <v>20484</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.23</v>
+        <v>1.07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.24</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="N2" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="O2" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="P2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S2" t="n">
+        <v>11</v>
+      </c>
+      <c r="T2" t="n">
         <v>13</v>
       </c>
-      <c r="R2" t="n">
-        <v>7</v>
-      </c>
-      <c r="S2" t="n">
-        <v>10</v>
-      </c>
-      <c r="T2" t="n">
-        <v>6</v>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>4fMAHvLm</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -826,185 +866,215 @@
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
-      <c r="AD2" t="n">
-        <v>27.22222222222222</v>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
       </c>
       <c r="AE2" t="n">
-        <v>183.2222222222222</v>
+        <v>26.2</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>181.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>76.55555555555556</v>
+        <v>1.4</v>
       </c>
       <c r="AH2" t="n">
-        <v>9666666.666666666</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AI2" t="n">
-        <v>78.77777777777777</v>
+        <v>6170000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>20.9</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AK2" t="n">
-        <v>184.1</v>
+        <v>24.9</v>
       </c>
       <c r="AL2" t="n">
-        <v>1</v>
+        <v>183</v>
       </c>
       <c r="AM2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>4532500</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>23.71428571428572</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>178.2142857142857</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="AT2" t="n">
         <v>70</v>
       </c>
-      <c r="AN2" t="n">
-        <v>4042500</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>23.15384615384615</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>181.0769230769231</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.307692307692308</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>73.30769230769231</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>6023076.923076923</v>
-      </c>
       <c r="AU2" t="n">
-        <v>80.30769230769231</v>
+        <v>2992857.142857143</v>
       </c>
       <c r="AV2" t="n">
-        <v>20.75</v>
+        <v>76.78571428571429</v>
       </c>
       <c r="AW2" t="n">
-        <v>182.1666666666667</v>
+        <v>24.73333333333333</v>
       </c>
       <c r="AX2" t="n">
-        <v>1</v>
+        <v>180.5333333333333</v>
       </c>
       <c r="AY2" t="n">
-        <v>67.5</v>
+        <v>1.266666666666667</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2800000</v>
+        <v>72.13333333333334</v>
       </c>
       <c r="BA2" t="n">
-        <v>77.33333333333333</v>
+        <v>4318333.333333333</v>
       </c>
       <c r="BB2" t="n">
-        <v>24.5</v>
+        <v>75.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>175</v>
+        <v>24.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>2</v>
+        <v>183.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>152</v>
+        <v>5</v>
       </c>
       <c r="BG2" t="n">
-        <v>22000000</v>
+        <v>356</v>
       </c>
       <c r="BH2" t="n">
-        <v>164</v>
+        <v>15100000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>378</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>26</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>179.2</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>355</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>15925000</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>369</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WlzDg17E</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45534.625</v>
+        <v>45535.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">petit a 
+          <t xml:space="preserve">angoula g 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">michel moretti stadium
-  ajaccio </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8470</v>
+        <v>15220</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2aeoANM8</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fsfAHubD</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.31</v>
+      </c>
       <c r="M3" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="N3" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="O3" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="P3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>4</v>
       </c>
-      <c r="S3" t="n">
-        <v>16</v>
-      </c>
       <c r="T3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>8tmnzqxe</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>4vG8dmrf</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="W3" t="n">
         <v>55</v>
       </c>
       <c r="X3" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -1012,168 +1082,202 @@
       <c r="Z3" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>12</v>
-      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="n">
-        <v>24.22222222222222</v>
-      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>182</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="AF3" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>74.55555555555556</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6755555.555555556</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>75.88888888888889</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>2278125</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>74.875</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>24.52941176470588</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>178.2352941176471</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.294117647058824</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>68.52941176470588</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3258823.529411765</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>73.41176470588235</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AY3" t="n">
         <v>1</v>
       </c>
-      <c r="AG3" t="n">
-        <v>64.66666666666667</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1016666.666666667</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>70.55555555555556</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>176.375</v>
-      </c>
-      <c r="AL3" t="n">
+      <c r="AZ3" t="n">
+        <v>68.13636363636364</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1545454.545454545</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>72.45454545454545</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>180</v>
+      </c>
+      <c r="BE3" t="n">
         <v>1</v>
       </c>
-      <c r="AM3" t="n">
-        <v>65.125</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1168750</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>70.875</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>176.1875</v>
-      </c>
-      <c r="AR3" t="n">
+      <c r="BF3" t="n">
         <v>1</v>
       </c>
-      <c r="AS3" t="n">
-        <v>65.8125</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>715625</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>70.0625</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>27.6875</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>181.25</v>
-      </c>
-      <c r="AX3" t="n">
+      <c r="BG3" t="n">
+        <v>76</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>82</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>183</v>
+      </c>
+      <c r="BL3" t="n">
         <v>1</v>
       </c>
-      <c r="AY3" t="n">
-        <v>65.625</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1020312.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BM3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>136</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>IoCT4kRP</t>
+          <t>zoZtwwYp</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45534.625</v>
+        <v>45535.39583333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">valnet a 
+          <t xml:space="preserve">gaillouste p 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade michel d ornano
-  caen </t>
+          <t xml:space="preserve">stade de la licorne
+  amiens </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20300</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>12097</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5460</v>
+      </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>GjLn2QoH</t>
+          <t>lKkBAsxF</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>25dB6Eto</t>
+          <t>jgNAYRGi</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="N4" t="n">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="O4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P4" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Q9EVqFe4</t>
+          <t>dS1CBple</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>SIiBpBrs</t>
+          <t>Cp0gM1r4</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -1189,155 +1293,181 @@
         <v>20242025</v>
       </c>
       <c r="AA4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AB4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="n">
-        <v>23.25</v>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
       </c>
       <c r="AE4" t="n">
-        <v>181.5</v>
+        <v>25.55555555555556</v>
       </c>
       <c r="AF4" t="n">
+        <v>178.5555555555555</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1</v>
       </c>
-      <c r="AG4" t="n">
-        <v>65.625</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1428125</v>
+        <v>65.88888888888889</v>
       </c>
       <c r="AI4" t="n">
-        <v>74.625</v>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
+        <v>1094444.444444444</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>71</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>178.2222222222222</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>71.22222222222223</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>4466666.666666667</v>
+      </c>
       <c r="AP4" t="n">
-        <v>26.72222222222222</v>
+        <v>77.44444444444444</v>
       </c>
       <c r="AQ4" t="n">
-        <v>183.8333333333333</v>
+        <v>25.61538461538462</v>
       </c>
       <c r="AR4" t="n">
+        <v>185.0769230769231</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.230769230769231</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>64.30769230769231</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>828846.1538461539</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>71.07692307692308</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>21.83333333333333</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>177.9166666666667</v>
+      </c>
+      <c r="AY4" t="n">
         <v>1</v>
       </c>
-      <c r="AS4" t="n">
-        <v>67.94444444444444</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1638888.888888889</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>72.66666666666667</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>179.3</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>61.2</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>680000</v>
+        <v>68.41666666666667</v>
       </c>
       <c r="BA4" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="BB4" t="inlineStr"/>
+        <v>2485416.666666667</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>77.25</v>
+      </c>
       <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>zyWS0tQi</t>
+          <t>8lUzaKf4</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45534.625</v>
+        <v>45535.39583333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">kubler g 
+          <t xml:space="preserve">batta f 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade gabriel montpied
-  clermont ferrand </t>
+          <t xml:space="preserve">stade saint symphorien
+  metz </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>10800</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>28786</v>
+      </c>
+      <c r="F5" t="n">
+        <v>18369</v>
+      </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>IRuMRua1</t>
+          <t>4v0yqlWc</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0OEHEprs</t>
+          <t>E1wDrLsJ</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="N5" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T5" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4G9MhScS</t>
+          <t>h89kUbu5</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>zB2j3YvM</t>
+          <t>Ys1Pb7ws</t>
         </is>
       </c>
       <c r="W5" t="n">
@@ -1356,708 +1486,88 @@
         <v>7</v>
       </c>
       <c r="AB5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="n">
-        <v>24.5</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>181.875</v>
+        <v>26.81818181818182</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.125</v>
+        <v>176.8181818181818</v>
       </c>
       <c r="AG5" t="n">
-        <v>68.125</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AH5" t="n">
-        <v>1715625</v>
+        <v>70.54545454545455</v>
       </c>
       <c r="AI5" t="n">
-        <v>74.5</v>
+        <v>1861363.636363636</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24.66666666666667</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>177.8888888888889</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>67.22222222222223</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1697222.222222222</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>71.55555555555556</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>22</v>
-      </c>
+        <v>73.90909090909091</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>176.125</v>
+        <v>21.3</v>
       </c>
       <c r="AR5" t="n">
+        <v>181.3</v>
+      </c>
+      <c r="AS5" t="n">
         <v>1</v>
       </c>
-      <c r="AS5" t="n">
-        <v>64.375</v>
-      </c>
       <c r="AT5" t="n">
-        <v>1425000</v>
+        <v>66.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>72.625</v>
+        <v>1797500</v>
       </c>
       <c r="AV5" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="AW5" t="n">
         <v>26.64285714285714</v>
       </c>
-      <c r="AW5" t="n">
-        <v>177.7857142857143</v>
-      </c>
       <c r="AX5" t="n">
-        <v>1.071428571428571</v>
+        <v>180.5714285714286</v>
       </c>
       <c r="AY5" t="n">
-        <v>67.21428571428571</v>
+        <v>1</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1314285.714285714</v>
+        <v>64.57142857142857</v>
       </c>
       <c r="BA5" t="n">
-        <v>69.78571428571429</v>
-      </c>
-      <c r="BB5" t="inlineStr"/>
+        <v>838571.4285714285</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>70.64285714285714</v>
+      </c>
       <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>06FhaTlm</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45534.625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rosier e 
-  fra </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade marcel tribut
-  dunkerque </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>4933</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>tAAobNse</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0pOdQOCg</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="n">
-        <v>52</v>
-      </c>
-      <c r="N6" t="n">
-        <v>48</v>
-      </c>
-      <c r="O6" t="n">
-        <v>13</v>
-      </c>
-      <c r="P6" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>9</v>
-      </c>
-      <c r="T6" t="n">
-        <v>14</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>lb31RXzP</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>OQuqpG7i</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>55</v>
-      </c>
-      <c r="X6" t="n">
-        <v>555</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="n">
-        <v>22.92307692307692</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>175.8461538461538</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>64.30769230769231</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1073076.923076923</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>73.23076923076923</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>21.30769230769231</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>184.0769230769231</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>62</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>726923.0769230769</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>71.30769230769231</v>
-      </c>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>UPVYr846</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45534.625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lesage m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade des alpes
-  grenoble </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>20068</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>UgPj1p1N</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>6NOhR4cm</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="n">
-        <v>49</v>
-      </c>
-      <c r="N7" t="n">
-        <v>51</v>
-      </c>
-      <c r="O7" t="n">
-        <v>7</v>
-      </c>
-      <c r="P7" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>5</v>
-      </c>
-      <c r="S7" t="n">
-        <v>8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>11</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>WrQARdPN</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>fm0Qb28B</t>
-        </is>
-      </c>
-      <c r="W7" t="n">
-        <v>55</v>
-      </c>
-      <c r="X7" t="n">
-        <v>555</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>185.7</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1597500</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>23.44444444444444</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>182.2222222222222</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>64.11111111111111</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>975000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>71.88888888888889</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>25.64285714285714</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>181</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.142857142857143</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>67.71428571428571</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1848214.285714286</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>73.42857142857143</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>27.88888888888889</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>177.6666666666667</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>65.33333333333333</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>736111.1111111111</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>69</v>
-      </c>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8WI0c7Ja</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45534.625</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chapapria r 
-  fra </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de roudourou
-  guingamp </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>19060</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>QDfKl36E</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2kM6ufaS</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="n">
-        <v>62</v>
-      </c>
-      <c r="N8" t="n">
-        <v>38</v>
-      </c>
-      <c r="O8" t="n">
-        <v>21</v>
-      </c>
-      <c r="P8" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>7</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7</v>
-      </c>
-      <c r="S8" t="n">
-        <v>12</v>
-      </c>
-      <c r="T8" t="n">
-        <v>10</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>QNSJnsB5</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>SzfSpYcf</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>55</v>
-      </c>
-      <c r="X8" t="n">
-        <v>555</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="n">
-        <v>24.11111111111111</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>179.8888888888889</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>65.33333333333333</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1077777.777777778</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>70.44444444444444</v>
-      </c>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="n">
-        <v>22.92857142857143</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>180.4285714285714</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>61.57142857142857</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>760714.2857142857</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>QiPssnZI</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45534.625</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">landry r 
-  fra </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>67394</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>ADl76OZP</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>AZwK8L6R</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>48</v>
-      </c>
-      <c r="N9" t="n">
-        <v>52</v>
-      </c>
-      <c r="O9" t="n">
-        <v>13</v>
-      </c>
-      <c r="P9" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>4</v>
-      </c>
-      <c r="S9" t="n">
-        <v>22</v>
-      </c>
-      <c r="T9" t="n">
-        <v>16</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>EwpPg8iH</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>fo8nHfg4</t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>55</v>
-      </c>
-      <c r="X9" t="n">
-        <v>555</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>179.5</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>967500</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>67</v>
-      </c>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP5"/>
+  <dimension ref="A1:BN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,210 +560,200 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>interceptions_home</t>
+          <t>id_team_home_rival_team</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>interceptions_away</t>
+          <t>id_team_away_rival_team</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>id_team_home_rival_team</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>id_team_away_rival_team</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>mean_val_player_start_home</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_pot_player_start_home</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_away</t>
+          <t>mean_val_player_start_away</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_pot_player_start_away</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_sub_home</t>
+          <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_sub_home</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_sub_home</t>
+          <t>mean_val_player_sub_home</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_sub_home</t>
+          <t>mean_pot_player_sub_home</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_sub_home</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_sub_home</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_sub_away</t>
+          <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_sub_away</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_sub_away</t>
+          <t>mean_val_player_sub_away</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_sub_away</t>
+          <t>mean_pot_player_sub_away</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_sub_away</t>
+          <t>mean_age_player_miss_home</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_sub_away</t>
+          <t>mean_hei_player_miss_home</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>mean_int_rep_player_miss_home</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>n_player_miss_home</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_home</t>
+          <t>sum_rat_player_miss_home</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>sum_val_player_miss_home</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>sum_pot_player_miss_home</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_home</t>
+          <t>mean_age_player_miss_away</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>mean_hei_player_miss_away</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_int_rep_player_miss_away</t>
         </is>
       </c>
       <c r="BK1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>n_player_miss_away</t>
         </is>
       </c>
       <c r="BL1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_away</t>
+          <t>sum_rat_player_miss_away</t>
         </is>
       </c>
       <c r="BM1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>sum_val_player_miss_away</t>
         </is>
       </c>
       <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
@@ -772,28 +762,30 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45536.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">millot b 
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>20484</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>50186</v>
+      </c>
+      <c r="F2" t="n">
+        <v>45434</v>
+      </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
@@ -802,52 +794,52 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.07</v>
+        <v>0.74</v>
       </c>
       <c r="L2" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="M2" t="n">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="O2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P2" t="n">
         <v>11</v>
       </c>
-      <c r="P2" t="n">
-        <v>10</v>
-      </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>nVS1TlC4</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -862,212 +854,208 @@
       <c r="Z2" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
+      <c r="AC2" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>181.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>26.2</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>181.2</v>
+        <v>75.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.4</v>
+        <v>11030000</v>
       </c>
       <c r="AH2" t="n">
-        <v>74.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="AI2" t="n">
-        <v>6170000</v>
+        <v>22.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>77.59999999999999</v>
+        <v>181.875</v>
       </c>
       <c r="AK2" t="n">
-        <v>24.9</v>
+        <v>2.125</v>
       </c>
       <c r="AL2" t="n">
-        <v>183</v>
+        <v>81.75</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.4</v>
+        <v>47000000</v>
       </c>
       <c r="AN2" t="n">
-        <v>72.2</v>
+        <v>86.75</v>
       </c>
       <c r="AO2" t="n">
-        <v>4532500</v>
+        <v>25.81818181818182</v>
       </c>
       <c r="AP2" t="n">
-        <v>75.90000000000001</v>
+        <v>176.3636363636364</v>
       </c>
       <c r="AQ2" t="n">
-        <v>23.71428571428572</v>
+        <v>1.818181818181818</v>
       </c>
       <c r="AR2" t="n">
-        <v>178.2142857142857</v>
+        <v>75.45454545454545</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.285714285714286</v>
+        <v>12288636.36363636</v>
       </c>
       <c r="AT2" t="n">
-        <v>70</v>
+        <v>79.18181818181819</v>
       </c>
       <c r="AU2" t="n">
-        <v>2992857.142857143</v>
+        <v>22.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>76.78571428571429</v>
+        <v>184.4444444444445</v>
       </c>
       <c r="AW2" t="n">
-        <v>24.73333333333333</v>
+        <v>1.944444444444444</v>
       </c>
       <c r="AX2" t="n">
-        <v>180.5333333333333</v>
+        <v>76.72222222222223</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.266666666666667</v>
+        <v>25327777.77777778</v>
       </c>
       <c r="AZ2" t="n">
-        <v>72.13333333333334</v>
+        <v>83.72222222222223</v>
       </c>
       <c r="BA2" t="n">
-        <v>4318333.333333333</v>
+        <v>29.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>75.2</v>
+        <v>179.75</v>
       </c>
       <c r="BC2" t="n">
-        <v>24.8</v>
+        <v>2</v>
       </c>
       <c r="BD2" t="n">
-        <v>183.8</v>
+        <v>4</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.2</v>
+        <v>307</v>
       </c>
       <c r="BF2" t="n">
-        <v>5</v>
+        <v>32800000</v>
       </c>
       <c r="BG2" t="n">
-        <v>356</v>
+        <v>307</v>
       </c>
       <c r="BH2" t="n">
-        <v>15100000</v>
+        <v>27</v>
       </c>
       <c r="BI2" t="n">
-        <v>378</v>
+        <v>186.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="BK2" t="n">
-        <v>179.2</v>
+        <v>2</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.4</v>
+        <v>165</v>
       </c>
       <c r="BM2" t="n">
-        <v>5</v>
+        <v>68000000</v>
       </c>
       <c r="BN2" t="n">
-        <v>355</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>15925000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>369</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45535.5</v>
+        <v>45536.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">angoula g 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>15220</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>18752</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9168</v>
+      </c>
       <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
         <v>4</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>1.47</v>
       </c>
       <c r="L3" t="n">
-        <v>0.31</v>
+        <v>2.56</v>
       </c>
       <c r="M3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="Q3" t="n">
         <v>7</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0tIbS515</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -1083,208 +1071,214 @@
         <v>20242025</v>
       </c>
       <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>183.2</v>
+      </c>
       <c r="AE3" t="n">
-        <v>27.33333333333333</v>
+        <v>1.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>179.3333333333333</v>
+        <v>67.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.333333333333333</v>
+        <v>1687500</v>
       </c>
       <c r="AH3" t="n">
-        <v>74.55555555555556</v>
+        <v>72.7</v>
       </c>
       <c r="AI3" t="n">
-        <v>6755555.555555556</v>
+        <v>22.77777777777778</v>
       </c>
       <c r="AJ3" t="n">
-        <v>75.88888888888889</v>
+        <v>181.5555555555555</v>
       </c>
       <c r="AK3" t="n">
-        <v>25.375</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AL3" t="n">
-        <v>181.75</v>
+        <v>74.22222222222223</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.125</v>
+        <v>10655555.55555556</v>
       </c>
       <c r="AN3" t="n">
-        <v>70.25</v>
+        <v>80.22222222222223</v>
       </c>
       <c r="AO3" t="n">
-        <v>2278125</v>
+        <v>27.65</v>
       </c>
       <c r="AP3" t="n">
-        <v>74.875</v>
+        <v>181.15</v>
       </c>
       <c r="AQ3" t="n">
-        <v>24.52941176470588</v>
+        <v>1.05</v>
       </c>
       <c r="AR3" t="n">
-        <v>178.2352941176471</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.294117647058824</v>
+        <v>1565000</v>
       </c>
       <c r="AT3" t="n">
-        <v>68.52941176470588</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>3258823.529411765</v>
+        <v>23.5625</v>
       </c>
       <c r="AV3" t="n">
-        <v>73.41176470588235</v>
+        <v>182.5625</v>
       </c>
       <c r="AW3" t="n">
-        <v>26.27272727272727</v>
+        <v>1.0625</v>
       </c>
       <c r="AX3" t="n">
-        <v>181.5</v>
+        <v>72.6875</v>
       </c>
       <c r="AY3" t="n">
-        <v>1</v>
+        <v>6451562.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>68.13636363636364</v>
+        <v>77.8125</v>
       </c>
       <c r="BA3" t="n">
-        <v>1545454.545454545</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="BB3" t="n">
-        <v>72.45454545454545</v>
+        <v>177.6666666666667</v>
       </c>
       <c r="BC3" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="BD3" t="n">
-        <v>180</v>
+        <v>3</v>
       </c>
       <c r="BE3" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="BF3" t="n">
-        <v>1</v>
+        <v>3300000</v>
       </c>
       <c r="BG3" t="n">
-        <v>76</v>
+        <v>213</v>
       </c>
       <c r="BH3" t="n">
-        <v>11500000</v>
+        <v>24.8</v>
       </c>
       <c r="BI3" t="n">
-        <v>82</v>
+        <v>180.4</v>
       </c>
       <c r="BJ3" t="n">
-        <v>25.5</v>
+        <v>1.8</v>
       </c>
       <c r="BK3" t="n">
-        <v>183</v>
+        <v>5</v>
       </c>
       <c r="BL3" t="n">
-        <v>1</v>
+        <v>373</v>
       </c>
       <c r="BM3" t="n">
-        <v>2</v>
+        <v>50400000</v>
       </c>
       <c r="BN3" t="n">
-        <v>136</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>3300000</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>144</v>
+        <v>393</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zoZtwwYp</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.39583333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gaillouste p 
+          <t xml:space="preserve">bollengier m 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la licorne
-  amiens </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>12097</v>
+        <v>25178</v>
       </c>
       <c r="F4" t="n">
-        <v>5460</v>
+        <v>19715</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>lKkBAsxF</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>jgNAYRGi</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.35</v>
+      </c>
       <c r="M4" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="O4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="P4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
       </c>
       <c r="T4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>dS1CBple</t>
+          <t>dWZTBmVT</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Cp0gM1r4</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>55</v>
       </c>
       <c r="X4" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1292,189 +1286,197 @@
       <c r="Z4" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>25.36363636363636</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>185.1818181818182</v>
       </c>
       <c r="AE4" t="n">
-        <v>25.55555555555556</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>178.5555555555555</v>
+        <v>71.18181818181819</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>2790909.090909091</v>
       </c>
       <c r="AH4" t="n">
-        <v>65.88888888888889</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1094444.444444444</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>71</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>23.77777777777778</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>178.2222222222222</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>71.22222222222223</v>
-      </c>
+        <v>74.90909090909091</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>4466666.666666667</v>
+        <v>23.53333333333333</v>
       </c>
       <c r="AP4" t="n">
-        <v>77.44444444444444</v>
+        <v>182</v>
       </c>
       <c r="AQ4" t="n">
-        <v>25.61538461538462</v>
+        <v>1</v>
       </c>
       <c r="AR4" t="n">
-        <v>185.0769230769231</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.230769230769231</v>
+        <v>2860000</v>
       </c>
       <c r="AT4" t="n">
-        <v>64.30769230769231</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AU4" t="n">
-        <v>828846.1538461539</v>
+        <v>22.80952380952381</v>
       </c>
       <c r="AV4" t="n">
-        <v>71.07692307692308</v>
+        <v>181.5238095238095</v>
       </c>
       <c r="AW4" t="n">
-        <v>21.83333333333333</v>
+        <v>1</v>
       </c>
       <c r="AX4" t="n">
-        <v>177.9166666666667</v>
+        <v>64.9047619047619</v>
       </c>
       <c r="AY4" t="n">
-        <v>1</v>
+        <v>1511904.761904762</v>
       </c>
       <c r="AZ4" t="n">
-        <v>68.41666666666667</v>
+        <v>71.9047619047619</v>
       </c>
       <c r="BA4" t="n">
-        <v>2485416.666666667</v>
+        <v>19</v>
       </c>
       <c r="BB4" t="n">
-        <v>77.25</v>
-      </c>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
+        <v>188</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>64</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>74</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>269</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>6350000</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>294</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8lUzaKf4</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.39583333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">batta f 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade saint symphorien
-  metz </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>28786</v>
-      </c>
-      <c r="F5" t="n">
-        <v>18369</v>
-      </c>
+        <v>21029</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4v0yqlWc</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>E1wDrLsJ</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.18</v>
+      </c>
       <c r="M5" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="N5" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="O5" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="P5" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q5" t="n">
         <v>7</v>
       </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>h89kUbu5</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Ys1Pb7ws</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>55</v>
       </c>
       <c r="X5" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1482,92 +1484,512 @@
       <c r="Z5" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="n">
-        <v>26.81818181818182</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>176.8181818181818</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.090909090909091</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>70.54545454545455</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1861363.636363636</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>73.90909090909091</v>
-      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
+      <c r="AO5" t="n">
+        <v>23.88235294117647</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>183.1176470588235</v>
+      </c>
       <c r="AQ5" t="n">
-        <v>21.3</v>
+        <v>1.058823529411765</v>
       </c>
       <c r="AR5" t="n">
-        <v>181.3</v>
+        <v>71.82352941176471</v>
       </c>
       <c r="AS5" t="n">
-        <v>1</v>
+        <v>6541176.470588235</v>
       </c>
       <c r="AT5" t="n">
-        <v>66.5</v>
+        <v>77.70588235294117</v>
       </c>
       <c r="AU5" t="n">
-        <v>1797500</v>
+        <v>24.14285714285714</v>
       </c>
       <c r="AV5" t="n">
-        <v>77.8</v>
+        <v>179.7142857142857</v>
       </c>
       <c r="AW5" t="n">
-        <v>26.64285714285714</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="AX5" t="n">
-        <v>180.5714285714286</v>
+        <v>72.92857142857143</v>
       </c>
       <c r="AY5" t="n">
-        <v>1</v>
+        <v>6760714.285714285</v>
       </c>
       <c r="AZ5" t="n">
-        <v>64.57142857142857</v>
+        <v>78.14285714285714</v>
       </c>
       <c r="BA5" t="n">
-        <v>838571.4285714285</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
-        <v>70.64285714285714</v>
-      </c>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
-      <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
+        <v>177.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>149</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>159</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>189</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>72</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45536.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9030</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="M6" t="n">
+        <v>61</v>
+      </c>
+      <c r="N6" t="n">
+        <v>39</v>
+      </c>
+      <c r="O6" t="n">
+        <v>14</v>
+      </c>
+      <c r="P6" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>11</v>
+      </c>
+      <c r="T6" t="n">
+        <v>21</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>55</v>
+      </c>
+      <c r="X6" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>183</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>11330000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>76</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>180.55</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>75.65000000000001</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>13997500</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>177.6111111111111</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.277777777777778</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>73</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>6472777.777777778</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>77.16666666666667</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>173</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>66</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>82</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>176.3333333333333</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>222</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>18100000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tYQyK8JN</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45535.66666666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F7" t="n">
+        <v>19178</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>24</v>
+      </c>
+      <c r="N7" t="n">
+        <v>76</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="n">
+        <v>15</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>55</v>
+      </c>
+      <c r="X7" t="n">
+        <v>551</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>23.55555555555556</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>5388888.888888889</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>78.11111111111111</v>
+      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>179.0666666666667</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>70.46666666666667</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3353333.333333333</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>76.53333333333333</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>178.625</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>15137500</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>182</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>135</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>5700000</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>153</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP12"/>
+  <dimension ref="A1:BP8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,82 +772,84 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CGH7Enso</t>
+          <t>Qw81zU34</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45549.58333333334</v>
+        <v>45550.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kherradji a 
+          <t xml:space="preserve">dechepy b 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17924</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>38223</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38116</v>
+      </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M2" t="n">
+        <v>54</v>
+      </c>
+      <c r="N2" t="n">
+        <v>46</v>
+      </c>
+      <c r="O2" t="n">
+        <v>12</v>
+      </c>
+      <c r="P2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R2" t="n">
         <v>3</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="M2" t="n">
-        <v>40</v>
-      </c>
-      <c r="N2" t="n">
-        <v>60</v>
-      </c>
-      <c r="O2" t="n">
-        <v>10</v>
-      </c>
-      <c r="P2" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R2" t="n">
-        <v>7</v>
       </c>
       <c r="S2" t="n">
         <v>12</v>
       </c>
       <c r="T2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>CWxpUrtf</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -864,208 +866,194 @@
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>24.81818181818182</v>
+        <v>26.36363636363636</v>
       </c>
       <c r="AF2" t="n">
-        <v>182.4545454545455</v>
+        <v>179.5454545454545</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="AH2" t="n">
-        <v>69.36363636363636</v>
+        <v>76.36363636363636</v>
       </c>
       <c r="AI2" t="n">
-        <v>2861363.636363636</v>
+        <v>11227272.72727273</v>
       </c>
       <c r="AJ2" t="n">
-        <v>73.45454545454545</v>
+        <v>79</v>
       </c>
       <c r="AK2" t="n">
-        <v>24</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="AL2" t="n">
-        <v>183.5</v>
+        <v>184.4444444444445</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.7</v>
+        <v>2.111111111111111</v>
       </c>
       <c r="AN2" t="n">
-        <v>76.5</v>
+        <v>76.88888888888889</v>
       </c>
       <c r="AO2" t="n">
-        <v>13600000</v>
+        <v>9833333.333333334</v>
       </c>
       <c r="AP2" t="n">
-        <v>81.3</v>
+        <v>78.33333333333333</v>
       </c>
       <c r="AQ2" t="n">
-        <v>24.4</v>
+        <v>23.15789473684211</v>
       </c>
       <c r="AR2" t="n">
-        <v>180.55</v>
+        <v>181.3157894736842</v>
       </c>
       <c r="AS2" t="n">
-        <v>1</v>
+        <v>1.105263157894737</v>
       </c>
       <c r="AT2" t="n">
-        <v>66.09999999999999</v>
+        <v>72.89473684210526</v>
       </c>
       <c r="AU2" t="n">
-        <v>1417500</v>
+        <v>7000000</v>
       </c>
       <c r="AV2" t="n">
-        <v>71.65000000000001</v>
+        <v>79.15789473684211</v>
       </c>
       <c r="AW2" t="n">
-        <v>22</v>
+        <v>24.26315789473684</v>
       </c>
       <c r="AX2" t="n">
-        <v>182.2</v>
+        <v>179.5263157894737</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.2</v>
+        <v>1.526315789473684</v>
       </c>
       <c r="AZ2" t="n">
-        <v>75.09999999999999</v>
+        <v>74.68421052631579</v>
       </c>
       <c r="BA2" t="n">
-        <v>15402500</v>
+        <v>9057894.736842105</v>
       </c>
       <c r="BB2" t="n">
-        <v>82.05</v>
+        <v>80.89473684210526</v>
       </c>
       <c r="BC2" t="n">
-        <v>22.25</v>
+        <v>29</v>
       </c>
       <c r="BD2" t="n">
-        <v>181.75</v>
+        <v>164</v>
       </c>
       <c r="BE2" t="n">
         <v>1</v>
       </c>
       <c r="BF2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BG2" t="n">
-        <v>266</v>
+        <v>72</v>
       </c>
       <c r="BH2" t="n">
-        <v>6650000</v>
+        <v>2100000</v>
       </c>
       <c r="BI2" t="n">
-        <v>299</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>183</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>140</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>10200000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>164</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0dMqm7mA</t>
+          <t>M51AY7YG</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45549.5</v>
+        <v>45550.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">millot b 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>67394</v>
+        <v>35322</v>
       </c>
       <c r="F3" t="n">
-        <v>65803</v>
+        <v>29811</v>
       </c>
       <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="L3" t="n">
-        <v>1.93</v>
+        <v>0.53</v>
       </c>
       <c r="M3" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="O3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="P3" t="n">
         <v>11</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
         <v>4</v>
       </c>
       <c r="S3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="T3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>pYizckpN</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -1084,210 +1072,194 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>lhUkVMh2</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>25.44444444444444</v>
+        <v>25.72727272727273</v>
       </c>
       <c r="AF3" t="n">
-        <v>181.3333333333333</v>
+        <v>181.3636363636364</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.444444444444444</v>
+        <v>1.454545454545455</v>
       </c>
       <c r="AH3" t="n">
-        <v>77.11111111111111</v>
+        <v>73.36363636363636</v>
       </c>
       <c r="AI3" t="n">
-        <v>15400000</v>
+        <v>5093181.818181818</v>
       </c>
       <c r="AJ3" t="n">
-        <v>79.44444444444444</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>182.3</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>75.3</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>11850000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>79.90000000000001</v>
-      </c>
+        <v>75.54545454545455</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>23.70588235294118</v>
+        <v>24.42105263157895</v>
       </c>
       <c r="AR3" t="n">
-        <v>182.3529411764706</v>
+        <v>182.6315789473684</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.235294117647059</v>
+        <v>1</v>
       </c>
       <c r="AT3" t="n">
-        <v>73.23529411764706</v>
+        <v>71.31578947368421</v>
       </c>
       <c r="AU3" t="n">
-        <v>7911764.705882353</v>
+        <v>3146052.631578947</v>
       </c>
       <c r="AV3" t="n">
-        <v>78.05882352941177</v>
+        <v>74.36842105263158</v>
       </c>
       <c r="AW3" t="n">
-        <v>22.45454545454545</v>
+        <v>23.875</v>
       </c>
       <c r="AX3" t="n">
-        <v>179.6818181818182</v>
+        <v>184.4375</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.318181818181818</v>
+        <v>1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>72.18181818181819</v>
+        <v>71.125</v>
       </c>
       <c r="BA3" t="n">
-        <v>7704545.454545454</v>
+        <v>5069375</v>
       </c>
       <c r="BB3" t="n">
-        <v>78.63636363636364</v>
+        <v>77.375</v>
       </c>
       <c r="BC3" t="n">
-        <v>20</v>
+        <v>27.66666666666667</v>
       </c>
       <c r="BD3" t="n">
-        <v>176.5</v>
+        <v>180.3333333333333</v>
       </c>
       <c r="BE3" t="n">
-        <v>1</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="BF3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>221</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>13200000</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>225</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM3" t="n">
         <v>2</v>
       </c>
-      <c r="BG3" t="n">
-        <v>137</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>156</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>182.8</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>5</v>
-      </c>
       <c r="BN3" t="n">
-        <v>369</v>
+        <v>149</v>
       </c>
       <c r="BO3" t="n">
-        <v>47750000</v>
+        <v>16000000</v>
       </c>
       <c r="BP3" t="n">
-        <v>383</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>vsYzkTIc</t>
+          <t>E3tkRPQj</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45548.65625</v>
+        <v>45550.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
+          <t xml:space="preserve">ben el hadj salem h 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>42000</v>
+        <v>26109</v>
       </c>
       <c r="F4" t="n">
-        <v>22144</v>
+        <v>19135</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="L4" t="n">
-        <v>1.11</v>
+        <v>0.75</v>
       </c>
       <c r="M4" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="N4" t="n">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="O4" t="n">
         <v>10</v>
       </c>
       <c r="P4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Q4" t="n">
         <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>nVS1TlC4</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -1304,209 +1276,215 @@
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>26.25</v>
+        <v>19.44444444444444</v>
       </c>
       <c r="AF4" t="n">
-        <v>182.125</v>
+        <v>183.3333333333333</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="AH4" t="n">
-        <v>71</v>
+        <v>70.66666666666667</v>
       </c>
       <c r="AI4" t="n">
-        <v>2475000</v>
+        <v>4566666.666666667</v>
       </c>
       <c r="AJ4" t="n">
-        <v>75.125</v>
+        <v>81.66666666666667</v>
       </c>
       <c r="AK4" t="n">
-        <v>25.5</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="AL4" t="n">
+        <v>181</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>69.33333333333333</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>2033333.333333333</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>73.22222222222223</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>21.0625</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>183.375</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>68.375</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2995312.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>78.125</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>25.05882352941176</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>180.9411764705882</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.058823529411765</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>65.64705882352941</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1167647.058823529</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>71.29411764705883</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD4" t="n">
         <v>183</v>
       </c>
-      <c r="AM4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>10050000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>79.8</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>25.61538461538462</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>182.3076923076923</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>68.15384615384616</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1640384.615384615</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>72.76923076923077</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>25.0625</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>178.6875</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>75.375</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>11090625</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>79.375</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>181.6666666666667</v>
-      </c>
       <c r="BE4" t="n">
         <v>1</v>
       </c>
       <c r="BF4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BG4" t="n">
-        <v>214</v>
+        <v>129</v>
       </c>
       <c r="BH4" t="n">
-        <v>5800000</v>
+        <v>2900000</v>
       </c>
       <c r="BI4" t="n">
-        <v>218</v>
+        <v>156</v>
       </c>
       <c r="BJ4" t="n">
-        <v>27.6</v>
+        <v>24.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>179.8</v>
+        <v>180.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BN4" t="n">
-        <v>379</v>
+        <v>130</v>
       </c>
       <c r="BO4" t="n">
-        <v>37800000</v>
+        <v>1700000</v>
       </c>
       <c r="BP4" t="n">
-        <v>390</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CtRiexfT</t>
+          <t>fJaIWo3T</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45549.39583333334</v>
+        <v>45550.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">leleu m 
+          <t xml:space="preserve">wattellier e 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade charlety
-  paris </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>33150</v>
+      </c>
+      <c r="F5" t="n">
+        <v>30097</v>
+      </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0OEHEprs</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.54</v>
+      </c>
       <c r="M5" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="N5" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="n">
         <v>7</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>zB2j3YvM</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>h89kUbu5</t>
+          <t>dWZTBmVT</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>55</v>
       </c>
       <c r="X5" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1514,131 +1492,151 @@
       <c r="Z5" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>16</v>
-      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>24.8</v>
+        <v>23.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>178.3</v>
+        <v>182.125</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.1</v>
+        <v>1.125</v>
       </c>
       <c r="AH5" t="n">
-        <v>67.3</v>
+        <v>72.75</v>
       </c>
       <c r="AI5" t="n">
-        <v>1657500</v>
+        <v>5525000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>71.2</v>
+        <v>77.875</v>
       </c>
       <c r="AK5" t="n">
-        <v>25.8</v>
+        <v>24.81818181818182</v>
       </c>
       <c r="AL5" t="n">
-        <v>177</v>
+        <v>183.8181818181818</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AN5" t="n">
-        <v>69.8</v>
+        <v>71.36363636363636</v>
       </c>
       <c r="AO5" t="n">
-        <v>1785000</v>
+        <v>3081818.181818182</v>
       </c>
       <c r="AP5" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="AQ5" t="n">
-        <v>26.77777777777778</v>
+        <v>23.17647058823529</v>
       </c>
       <c r="AR5" t="n">
-        <v>177.3333333333333</v>
+        <v>180.6470588235294</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.055555555555556</v>
+        <v>1</v>
       </c>
       <c r="AT5" t="n">
-        <v>69.22222222222223</v>
+        <v>71</v>
       </c>
       <c r="AU5" t="n">
-        <v>4211111.111111111</v>
+        <v>3405882.352941176</v>
       </c>
       <c r="AV5" t="n">
-        <v>71.88888888888889</v>
+        <v>77.41176470588235</v>
       </c>
       <c r="AW5" t="n">
-        <v>25.07692307692308</v>
+        <v>25.65</v>
       </c>
       <c r="AX5" t="n">
-        <v>177.4615384615385</v>
+        <v>182</v>
       </c>
       <c r="AY5" t="n">
         <v>1</v>
       </c>
       <c r="AZ5" t="n">
-        <v>68.53846153846153</v>
+        <v>69.7</v>
       </c>
       <c r="BA5" t="n">
-        <v>1753846.153846154</v>
+        <v>2060000</v>
       </c>
       <c r="BB5" t="n">
-        <v>73.15384615384616</v>
-      </c>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
-      <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
+        <v>72.95</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>178</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>78</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>188</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>64</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WjsR9y9M</t>
+          <t>hCffxjZi</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45548.625</v>
+        <v>45550.41666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">angoula g 
+          <t xml:space="preserve">pignard j 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc des sports
-  annecy </t>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>15660</v>
+        <v>29778</v>
       </c>
       <c r="F6" t="n">
-        <v>5478</v>
+        <v>27451</v>
       </c>
       <c r="G6" t="n">
         <v>3</v>
@@ -1648,55 +1646,59 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25dB6Eto</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>lKkBAsxF</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.31</v>
+      </c>
       <c r="M6" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="N6" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="O6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P6" t="n">
         <v>12</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
         <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="T6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SIiBpBrs</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>dS1CBple</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>55</v>
       </c>
       <c r="X6" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1704,185 +1706,221 @@
       <c r="Z6" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
       <c r="AE6" t="n">
-        <v>27.25</v>
+        <v>25.4</v>
       </c>
       <c r="AF6" t="n">
-        <v>181.25</v>
+        <v>180.2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="AH6" t="n">
-        <v>64.5</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AI6" t="n">
-        <v>681250</v>
+        <v>8330000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>67</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AK6" t="n">
-        <v>26.4</v>
+        <v>24.88888888888889</v>
       </c>
       <c r="AL6" t="n">
-        <v>182.8</v>
+        <v>179.6666666666667</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.1</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AN6" t="n">
-        <v>67.2</v>
+        <v>72.66666666666667</v>
       </c>
       <c r="AO6" t="n">
-        <v>1182500</v>
+        <v>5433333.333333333</v>
       </c>
       <c r="AP6" t="n">
-        <v>72.09999999999999</v>
+        <v>77.66666666666667</v>
       </c>
       <c r="AQ6" t="n">
-        <v>22.27272727272727</v>
+        <v>22.05263157894737</v>
       </c>
       <c r="AR6" t="n">
-        <v>179.3636363636364</v>
+        <v>178.8421052631579</v>
       </c>
       <c r="AS6" t="n">
-        <v>1</v>
+        <v>1.368421052631579</v>
       </c>
       <c r="AT6" t="n">
-        <v>61.63636363636363</v>
+        <v>71.15789473684211</v>
       </c>
       <c r="AU6" t="n">
-        <v>677272.7272727273</v>
+        <v>6905263.157894737</v>
       </c>
       <c r="AV6" t="n">
-        <v>70</v>
+        <v>78.10526315789474</v>
       </c>
       <c r="AW6" t="n">
-        <v>23.86666666666667</v>
+        <v>26.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>178.6666666666667</v>
+        <v>179.3333333333333</v>
       </c>
       <c r="AY6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>64.66666666666667</v>
+        <v>71.83333333333333</v>
       </c>
       <c r="BA6" t="n">
-        <v>1143333.333333333</v>
+        <v>3516666.666666667</v>
       </c>
       <c r="BB6" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
-      <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
+        <v>76.25</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>187</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>145</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>8400000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>158</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>185.6</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>358</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>19600000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>383</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SGTLiuxR</t>
+          <t>8MPiooIM</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45548.625</v>
+        <v>45549.66666666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisard j 
+          <t xml:space="preserve">turpin c 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade armand cesari
-  bastia </t>
+          <t xml:space="preserve">parc des princes
+  paris </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16048</v>
+        <v>48229</v>
       </c>
       <c r="F7" t="n">
-        <v>10567</v>
+        <v>47628</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AZwK8L6R</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fsfAHubD</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.93</v>
+      </c>
       <c r="M7" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="N7" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="O7" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="n">
+        <v>9</v>
+      </c>
+      <c r="R7" t="n">
         <v>3</v>
       </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>fo8nHfg4</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>4vG8dmrf</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>55</v>
       </c>
       <c r="X7" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1890,166 +1928,202 @@
       <c r="Z7" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>7</v>
-      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
+      <c r="AE7" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>82</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>43812500</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>85.125</v>
+      </c>
       <c r="AK7" t="n">
-        <v>24.66666666666667</v>
+        <v>27.9</v>
       </c>
       <c r="AL7" t="n">
-        <v>179.2222222222222</v>
+        <v>182.6</v>
       </c>
       <c r="AM7" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>66.55555555555556</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="AO7" t="n">
-        <v>1405555.555555556</v>
+        <v>6170000</v>
       </c>
       <c r="AP7" t="n">
-        <v>72.11111111111111</v>
+        <v>76</v>
       </c>
       <c r="AQ7" t="n">
-        <v>25.35714285714286</v>
+        <v>21.375</v>
       </c>
       <c r="AR7" t="n">
-        <v>178.3571428571429</v>
+        <v>183.75</v>
       </c>
       <c r="AS7" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="AT7" t="n">
-        <v>64.14285714285714</v>
+        <v>76.375</v>
       </c>
       <c r="AU7" t="n">
-        <v>880357.1428571428</v>
+        <v>28337500</v>
       </c>
       <c r="AV7" t="n">
-        <v>67.42857142857143</v>
+        <v>84.875</v>
       </c>
       <c r="AW7" t="n">
-        <v>24.66666666666667</v>
+        <v>25.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>178.8888888888889</v>
+        <v>180.8636363636364</v>
       </c>
       <c r="AY7" t="n">
-        <v>1</v>
+        <v>1.227272727272727</v>
       </c>
       <c r="AZ7" t="n">
-        <v>66.44444444444444</v>
+        <v>72</v>
       </c>
       <c r="BA7" t="n">
-        <v>1345833.333333333</v>
+        <v>4059090.909090909</v>
       </c>
       <c r="BB7" t="n">
-        <v>72.38888888888889</v>
-      </c>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
-      <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
+        <v>75.09090909090909</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>326</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>147500000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>343</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>183</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>154</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>23500000</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jyOc4FWq</t>
+          <t>4GNqcbPG</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45548.625</v>
+        <v>45551.65625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">benchabane f 
+          <t xml:space="preserve">thual o 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade gabriel montpied
-  clermont ferrand </t>
+          <t xml:space="preserve">stade des alpes
+  grenoble </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10800</v>
+        <v>20068</v>
       </c>
       <c r="F8" t="n">
-        <v>4275</v>
+        <v>4079</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IRuMRua1</t>
+          <t>UgPj1p1N</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>tAAobNse</t>
+          <t>GjLn2QoH</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N8" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O8" t="n">
+        <v>12</v>
+      </c>
+      <c r="P8" t="n">
         <v>6</v>
       </c>
-      <c r="P8" t="n">
-        <v>8</v>
-      </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
         <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>4G9MhScS</t>
+          <t>WrQARdPN</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>lb31RXzP</t>
+          <t>Q9EVqFe4</t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -2065,72 +2139,84 @@
         <v>20242025</v>
       </c>
       <c r="AA8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB8" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
-        <v>22.77777777777778</v>
+        <v>26.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>181</v>
+        <v>185.6</v>
       </c>
       <c r="AG8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1527500</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>71</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>25.22222222222222</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>180.1111111111111</v>
+      </c>
+      <c r="AM8" t="n">
         <v>1.111111111111111</v>
       </c>
-      <c r="AH8" t="n">
-        <v>65.11111111111111</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>74.11111111111111</v>
-      </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
+      <c r="AN8" t="n">
+        <v>67.88888888888889</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1877777.777777778</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>73.88888888888889</v>
+      </c>
       <c r="AQ8" t="n">
-        <v>23.76923076923077</v>
+        <v>24.64705882352941</v>
       </c>
       <c r="AR8" t="n">
-        <v>176.9230769230769</v>
+        <v>186.1176470588235</v>
       </c>
       <c r="AS8" t="n">
         <v>1</v>
       </c>
       <c r="AT8" t="n">
-        <v>66.61538461538461</v>
+        <v>65.47058823529412</v>
       </c>
       <c r="AU8" t="n">
-        <v>1563461.538461538</v>
+        <v>1447058.823529412</v>
       </c>
       <c r="AV8" t="n">
-        <v>71.61538461538461</v>
+        <v>71.29411764705883</v>
       </c>
       <c r="AW8" t="n">
-        <v>25.8</v>
+        <v>24.8125</v>
       </c>
       <c r="AX8" t="n">
-        <v>179</v>
+        <v>185.125</v>
       </c>
       <c r="AY8" t="n">
         <v>1</v>
       </c>
       <c r="AZ8" t="n">
-        <v>64.59999999999999</v>
+        <v>65.5625</v>
       </c>
       <c r="BA8" t="n">
-        <v>957500</v>
+        <v>1184375</v>
       </c>
       <c r="BB8" t="n">
-        <v>70.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
@@ -2147,694 +2233,6 @@
       <c r="BO8" t="inlineStr"/>
       <c r="BP8" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>xU3hQdg3</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45548.625</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">taleb a 
-  fra </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade francis le basser
-  laval </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>11017</v>
-      </c>
-      <c r="F9" t="n">
-        <v>5748</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>E1wDrLsJ</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2aeoANM8</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>47</v>
-      </c>
-      <c r="N9" t="n">
-        <v>53</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>5</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Ys1Pb7ws</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>8tmnzqxe</t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>55</v>
-      </c>
-      <c r="X9" t="n">
-        <v>555</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>179.7</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1002500</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>28.66666666666667</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>182.1333333333333</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>66.53333333333333</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1054333.333333333</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>71</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>23.95454545454545</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>179.5909090909091</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>63.59090909090909</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>809090.9090909091</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>69.77272727272727</v>
-      </c>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
-      <c r="BI9" t="inlineStr"/>
-      <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
-      <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>dYQ52g1d</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45548.625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">legat p 
-  fra </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade du moustoir
-  lorient </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>16787</v>
-      </c>
-      <c r="F10" t="n">
-        <v>10017</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>jgNAYRGi</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2kM6ufaS</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
-        <v>53</v>
-      </c>
-      <c r="N10" t="n">
-        <v>47</v>
-      </c>
-      <c r="O10" t="n">
-        <v>14</v>
-      </c>
-      <c r="P10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>7</v>
-      </c>
-      <c r="R10" t="n">
-        <v>3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="n">
-        <v>12</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Cp0gM1r4</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>SzfSpYcf</t>
-        </is>
-      </c>
-      <c r="W10" t="n">
-        <v>55</v>
-      </c>
-      <c r="X10" t="n">
-        <v>555</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>179.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>4150000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="n">
-        <v>22.125</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>176.75</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>68.625</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2440625</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>77.625</v>
-      </c>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="inlineStr"/>
-      <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="inlineStr"/>
-      <c r="BM10" t="inlineStr"/>
-      <c r="BN10" t="inlineStr"/>
-      <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>bwqJBcvA</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45548.625</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bouille t 
-  fra </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nouste camp
-  pau </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>4031</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2741</v>
-      </c>
-      <c r="G11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>6NOhR4cm</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ADl76OZP</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
-        <v>54</v>
-      </c>
-      <c r="N11" t="n">
-        <v>46</v>
-      </c>
-      <c r="O11" t="n">
-        <v>19</v>
-      </c>
-      <c r="P11" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>9</v>
-      </c>
-      <c r="R11" t="n">
-        <v>3</v>
-      </c>
-      <c r="S11" t="n">
-        <v>15</v>
-      </c>
-      <c r="T11" t="n">
-        <v>17</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>fm0Qb28B</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>EwpPg8iH</t>
-        </is>
-      </c>
-      <c r="W11" t="n">
-        <v>55</v>
-      </c>
-      <c r="X11" t="n">
-        <v>555</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="n">
-        <v>25.25</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>185</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>64.75</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>928125</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>70.875</v>
-      </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="n">
-        <v>25.53846153846154</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>180.7692307692308</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>65.07692307692308</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>917307.6923076923</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>71.61538461538461</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>184.6</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>880000</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
-      <c r="BI11" t="inlineStr"/>
-      <c r="BJ11" t="inlineStr"/>
-      <c r="BK11" t="inlineStr"/>
-      <c r="BL11" t="inlineStr"/>
-      <c r="BM11" t="inlineStr"/>
-      <c r="BN11" t="inlineStr"/>
-      <c r="BO11" t="inlineStr"/>
-      <c r="BP11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2BkADJ9c</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45548.625</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">petit a 
-  fra </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade paul lignon
-  rodez </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>5955</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3991</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0pOdQOCg</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>QDfKl36E</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="n">
-        <v>45</v>
-      </c>
-      <c r="N12" t="n">
-        <v>55</v>
-      </c>
-      <c r="O12" t="n">
-        <v>4</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>OQuqpG7i</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>QNSJnsB5</t>
-        </is>
-      </c>
-      <c r="W12" t="n">
-        <v>55</v>
-      </c>
-      <c r="X12" t="n">
-        <v>555</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>180.3</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1050000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>25.76923076923077</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>185</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>63.53846153846154</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>626923.0769230769</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>68.92307692307692</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>22.45454545454545</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>179.9090909090909</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>61.90909090909091</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>895454.5454545454</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>71.09090909090909</v>
-      </c>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
-      <c r="BI12" t="inlineStr"/>
-      <c r="BJ12" t="inlineStr"/>
-      <c r="BK12" t="inlineStr"/>
-      <c r="BL12" t="inlineStr"/>
-      <c r="BM12" t="inlineStr"/>
-      <c r="BN12" t="inlineStr"/>
-      <c r="BO12" t="inlineStr"/>
-      <c r="BP12" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF8"/>
+  <dimension ref="A1:CT11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,240 +610,310 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>red_cards_home</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>red_cards_away</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>total_passes_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>total_passes_away</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>completed_passes_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>completed_passes_away</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>clearances_completed_home</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>clearances_completed_away</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>crosses_completed_home</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>crosses_completed_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>interceptions_home</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>interceptions_away</t>
-        </is>
-      </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_start_home</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_home</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_home</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_home</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_home</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_away</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_start_away</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_start_away</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_home</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_home</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_home</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_home</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_home</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_away</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_sub_away</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_home</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_home</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_home</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_home</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_home</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_home</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_home</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_home</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_away</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_away</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_away</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_away</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_away</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_away</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_away</t>
         </is>
@@ -852,165 +922,193 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>OAZJOoNr</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45571.65625</v>
+        <v>45584.58333333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisard j 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>36178</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30247</v>
-      </c>
+        <v>42000</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.53</v>
+        <v>0.72</v>
       </c>
       <c r="L2" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="M2" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="N2" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="O2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="P2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>16</v>
+      </c>
+      <c r="X2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
         <v>3</v>
       </c>
-      <c r="R2" t="n">
-        <v>9</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="AC2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE2" t="n">
         <v>3</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>331</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>568</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>248</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP2" t="n">
         <v>5</v>
       </c>
-      <c r="U2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V2" t="n">
-        <v>5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>9</v>
-      </c>
-      <c r="X2" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC2" t="n">
+      <c r="AQ2" t="n">
         <v>11</v>
       </c>
-      <c r="AD2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
+      <c r="AR2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
         <v>55</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AV2" t="n">
         <v>551</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AW2" t="n">
         <v>0</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AX2" t="n">
         <v>20242025</v>
       </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
+      <c r="BC2" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>70.625</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>5875</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2475000</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1</v>
+      </c>
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="inlineStr"/>
@@ -1018,13 +1116,27 @@
       <c r="BN2" t="inlineStr"/>
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr"/>
-      <c r="BW2" t="inlineStr"/>
+      <c r="BQ2" t="n">
+        <v>24.73333333333333</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>68</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>3800</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1768333.333333333</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>73.26666666666667</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1</v>
+      </c>
       <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="inlineStr"/>
@@ -1032,21 +1144,51 @@
       <c r="CB2" t="inlineStr"/>
       <c r="CC2" t="inlineStr"/>
       <c r="CD2" t="inlineStr"/>
-      <c r="CE2" t="inlineStr"/>
-      <c r="CF2" t="inlineStr"/>
+      <c r="CE2" t="n">
+        <v>28</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>280</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>6675000</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>284</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CM2" t="inlineStr"/>
+      <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="inlineStr"/>
+      <c r="CS2" t="inlineStr"/>
+      <c r="CT2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>WzwSMPie</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45571.5</v>
+        <v>45584.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">millot b 
+          <t xml:space="preserve">dechepy b 
   fra </t>
         </is>
       </c>
@@ -1059,14 +1201,12 @@
       <c r="E3" t="n">
         <v>15220</v>
       </c>
-      <c r="F3" t="n">
-        <v>14572</v>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1075,121 +1215,133 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.77</v>
+        <v>1.32</v>
       </c>
       <c r="L3" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="M3" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="N3" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P3" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
         <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>459</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>365</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>353</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>292</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>9</v>
       </c>
-      <c r="AA3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC3" t="n">
+      <c r="AR3" t="n">
         <v>11</v>
       </c>
-      <c r="AD3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE3" t="n">
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW3" t="n">
         <v>0</v>
       </c>
-      <c r="AF3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>dWZTBmVT</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>551</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
+      <c r="AX3" t="n">
         <v>20242025</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
@@ -1224,160 +1376,210 @@
       <c r="CD3" t="inlineStr"/>
       <c r="CE3" t="inlineStr"/>
       <c r="CF3" t="inlineStr"/>
+      <c r="CG3" t="inlineStr"/>
+      <c r="CH3" t="inlineStr"/>
+      <c r="CI3" t="inlineStr"/>
+      <c r="CJ3" t="inlineStr"/>
+      <c r="CK3" t="inlineStr"/>
+      <c r="CL3" t="inlineStr"/>
+      <c r="CM3" t="n">
+        <v>20</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>189</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>72</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>78</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>vwbmU7aL</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45571.5</v>
+        <v>45583.65625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bastien b 
+          <t xml:space="preserve">wattellier e 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>21029</v>
+        <v>18523</v>
       </c>
       <c r="F4" t="n">
-        <v>14903</v>
+        <v>7246</v>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M4" t="n">
+        <v>51</v>
+      </c>
+      <c r="N4" t="n">
+        <v>49</v>
+      </c>
+      <c r="O4" t="n">
+        <v>14</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
         <v>4</v>
       </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="M4" t="n">
-        <v>48</v>
-      </c>
-      <c r="N4" t="n">
-        <v>52</v>
-      </c>
-      <c r="O4" t="n">
-        <v>18</v>
-      </c>
-      <c r="P4" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5</v>
-      </c>
       <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
         <v>3</v>
       </c>
-      <c r="S4" t="n">
-        <v>8</v>
-      </c>
-      <c r="T4" t="n">
-        <v>5</v>
-      </c>
-      <c r="U4" t="n">
-        <v>5</v>
-      </c>
       <c r="V4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
+        <v>14</v>
+      </c>
+      <c r="X4" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD4" t="n">
         <v>17</v>
       </c>
-      <c r="X4" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y4" t="n">
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
         <v>4</v>
       </c>
-      <c r="Z4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AG4" t="n">
         <v>13</v>
       </c>
-      <c r="AD4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>15</v>
-      </c>
       <c r="AH4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ4" t="n">
         <v>5</v>
       </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
-        </is>
+      <c r="AK4" t="n">
+        <v>458</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>444</v>
       </c>
       <c r="AM4" t="n">
+        <v>385</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>358</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
         <v>55</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AV4" t="n">
         <v>551</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AW4" t="n">
         <v>0</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AX4" t="n">
         <v>20242025</v>
       </c>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
+      <c r="AY4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
@@ -1410,169 +1612,219 @@
       <c r="CD4" t="inlineStr"/>
       <c r="CE4" t="inlineStr"/>
       <c r="CF4" t="inlineStr"/>
+      <c r="CG4" t="inlineStr"/>
+      <c r="CH4" t="inlineStr"/>
+      <c r="CI4" t="inlineStr"/>
+      <c r="CJ4" t="inlineStr"/>
+      <c r="CK4" t="inlineStr"/>
+      <c r="CL4" t="inlineStr"/>
+      <c r="CM4" t="n">
+        <v>28</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>187</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>75</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>76</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>xlCidXdD</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45571.5</v>
+        <v>45584.375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">frappart s 
+          <t xml:space="preserve">taleb a 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
+          <t xml:space="preserve">stade de la licorne
+  amiens </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>26109</v>
+        <v>12097</v>
       </c>
       <c r="F5" t="n">
-        <v>19968</v>
+        <v>5956</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>lKkBAsxF</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.96</v>
-      </c>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="N5" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="O5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="P5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
       </c>
       <c r="T5" t="n">
+        <v>8</v>
+      </c>
+      <c r="U5" t="n">
         <v>3</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
+        <v>2</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="n">
         <v>0</v>
       </c>
-      <c r="V5" t="n">
-        <v>4</v>
-      </c>
-      <c r="W5" t="n">
-        <v>22</v>
-      </c>
-      <c r="X5" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>18</v>
-      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
         <v>3</v>
       </c>
       <c r="AF5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AG5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
         <v>18</v>
       </c>
       <c r="AI5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>K6b7RoBp</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>363</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>506</v>
       </c>
       <c r="AM5" t="n">
+        <v>274</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>409</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
         <v>55</v>
       </c>
-      <c r="AN5" t="n">
-        <v>551</v>
-      </c>
-      <c r="AO5" t="n">
+      <c r="AV5" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW5" t="n">
         <v>0</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AX5" t="n">
         <v>20242025</v>
       </c>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
+      <c r="BA5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>177.2</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>65.7</v>
+      </c>
       <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
+      <c r="BG5" t="n">
+        <v>1125000</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1</v>
+      </c>
       <c r="BJ5" t="inlineStr"/>
       <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="inlineStr"/>
@@ -1580,194 +1832,254 @@
       <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="inlineStr"/>
-      <c r="BQ5" t="inlineStr"/>
-      <c r="BR5" t="inlineStr"/>
-      <c r="BS5" t="inlineStr"/>
+      <c r="BQ5" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>184.4166666666667</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>65.91666666666667</v>
+      </c>
       <c r="BT5" t="inlineStr"/>
-      <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="inlineStr"/>
-      <c r="BW5" t="inlineStr"/>
-      <c r="BX5" t="inlineStr"/>
+      <c r="BU5" t="n">
+        <v>1137500</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>24.92307692307692</v>
+      </c>
       <c r="BY5" t="n">
-        <v>20</v>
+        <v>179.1538461538462</v>
       </c>
       <c r="BZ5" t="n">
-        <v>184</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>1</v>
-      </c>
+        <v>63.46153846153846</v>
+      </c>
+      <c r="CA5" t="inlineStr"/>
       <c r="CB5" t="n">
-        <v>64</v>
+        <v>646153.8461538461</v>
       </c>
       <c r="CC5" t="n">
-        <v>6000</v>
+        <v>69.30769230769231</v>
       </c>
       <c r="CD5" t="n">
-        <v>1400000</v>
+        <v>1</v>
       </c>
       <c r="CE5" t="n">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="CF5" t="n">
-        <v>1</v>
+        <v>177.5</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>117</v>
+      </c>
+      <c r="CI5" t="inlineStr"/>
+      <c r="CJ5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>150</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>180.8</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>5</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>339</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>14000</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>4325000</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>346</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>lbfDWDYP</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45583.625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bollengier m 
+          <t xml:space="preserve">pignard j 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
+          <t xml:space="preserve">stade armand cesari
+  bastia </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>59186</v>
+        <v>16048</v>
       </c>
       <c r="F6" t="n">
-        <v>51888</v>
+        <v>9967</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>AZwK8L6R</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.76</v>
-      </c>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="N6" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="O6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="n">
         <v>11</v>
       </c>
-      <c r="Q6" t="n">
-        <v>6</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6</v>
-      </c>
-      <c r="S6" t="n">
-        <v>8</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W6" t="n">
+      <c r="Z6" t="n">
         <v>5</v>
       </c>
-      <c r="X6" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>29</v>
-      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
         <v>4</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AH6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>525</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>363</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>444</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>262</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP6" t="n">
         <v>5</v>
       </c>
-      <c r="AI6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-      <c r="AM6" t="n">
+      <c r="AQ6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
         <v>55</v>
       </c>
-      <c r="AN6" t="n">
-        <v>551</v>
-      </c>
-      <c r="AO6" t="n">
+      <c r="AV6" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW6" t="n">
         <v>0</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AX6" t="n">
         <v>20242025</v>
       </c>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>18</v>
+      </c>
       <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="inlineStr"/>
@@ -1782,13 +2094,25 @@
       <c r="BN6" t="inlineStr"/>
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
+      <c r="BQ6" t="n">
+        <v>24.21428571428572</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>180.4285714285714</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>61.71428571428572</v>
+      </c>
       <c r="BT6" t="inlineStr"/>
-      <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
-      <c r="BW6" t="inlineStr"/>
+      <c r="BU6" t="n">
+        <v>610714.2857142857</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>66.07142857142857</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1</v>
+      </c>
       <c r="BX6" t="inlineStr"/>
       <c r="BY6" t="inlineStr"/>
       <c r="BZ6" t="inlineStr"/>
@@ -1796,171 +2120,221 @@
       <c r="CB6" t="inlineStr"/>
       <c r="CC6" t="inlineStr"/>
       <c r="CD6" t="inlineStr"/>
-      <c r="CE6" t="inlineStr"/>
-      <c r="CF6" t="inlineStr"/>
+      <c r="CE6" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>179</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>131</v>
+      </c>
+      <c r="CI6" t="inlineStr"/>
+      <c r="CJ6" t="n">
+        <v>1825000</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>142</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM6" t="inlineStr"/>
+      <c r="CN6" t="inlineStr"/>
+      <c r="CO6" t="inlineStr"/>
+      <c r="CP6" t="inlineStr"/>
+      <c r="CQ6" t="inlineStr"/>
+      <c r="CR6" t="inlineStr"/>
+      <c r="CS6" t="inlineStr"/>
+      <c r="CT6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>8Kp3c9Oq</t>
+          <t>d47R8AtJ</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45570.66666666666</v>
+        <v>45583.625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">benchabane f 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
+          <t xml:space="preserve">stade des alpes
+  grenoble </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>29778</v>
+        <v>20068</v>
       </c>
       <c r="F7" t="n">
-        <v>26533</v>
+        <v>5916</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>UgPj1p1N</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.59</v>
-      </c>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="N7" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="O7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P7" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q7" t="n">
         <v>5</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
+        <v>7</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="n">
         <v>3</v>
       </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
+      <c r="Z7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>338</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>632</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>548</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP7" t="n">
         <v>6</v>
       </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>19</v>
-      </c>
-      <c r="X7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE7" t="n">
+      <c r="AQ7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW7" t="n">
         <v>0</v>
       </c>
-      <c r="AF7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-      <c r="AM7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>551</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
+      <c r="AX7" t="n">
         <v>20242025</v>
       </c>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
+      <c r="BA7" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>26.22222222222222</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>184.2222222222222</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>67.11111111111111</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2888.888888888889</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>70.44444444444444</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1</v>
+      </c>
       <c r="BJ7" t="inlineStr"/>
       <c r="BK7" t="inlineStr"/>
       <c r="BL7" t="inlineStr"/>
@@ -1969,263 +2343,1113 @@
       <c r="BO7" t="inlineStr"/>
       <c r="BP7" t="inlineStr"/>
       <c r="BQ7" t="n">
-        <v>20</v>
+        <v>23.22222222222222</v>
       </c>
       <c r="BR7" t="n">
-        <v>189</v>
+        <v>181.3333333333333</v>
       </c>
       <c r="BS7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>72</v>
-      </c>
+        <v>64.5</v>
+      </c>
+      <c r="BT7" t="inlineStr"/>
       <c r="BU7" t="n">
-        <v>14000</v>
+        <v>1454166.666666667</v>
       </c>
       <c r="BV7" t="n">
-        <v>2900000</v>
+        <v>71.44444444444444</v>
       </c>
       <c r="BW7" t="n">
-        <v>78</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="inlineStr"/>
       <c r="CA7" t="inlineStr"/>
       <c r="CB7" t="inlineStr"/>
       <c r="CC7" t="inlineStr"/>
       <c r="CD7" t="inlineStr"/>
-      <c r="CE7" t="inlineStr"/>
-      <c r="CF7" t="inlineStr"/>
+      <c r="CE7" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>139</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>139</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>23</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>186</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>69</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>75</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>fPQD76ac</t>
+          <t>4zEqbgS0</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45570.625</v>
+        <v>45583.625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">paradis g 
+          <t xml:space="preserve">rosier e 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade saint symphorien
-  metz </t>
+          <t xml:space="preserve">stade de roudourou
+  guingamp </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>28786</v>
+        <v>19060</v>
       </c>
       <c r="F8" t="n">
-        <v>18279</v>
+        <v>8112</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4v0yqlWc</t>
+          <t>QDfKl36E</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>lKkBAsxF</t>
+          <t>6NOhR4cm</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N8" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="O8" t="n">
         <v>15</v>
       </c>
       <c r="P8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q8" t="n">
         <v>6</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>7</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
+        <v>7</v>
+      </c>
+      <c r="T8" t="n">
         <v>4</v>
       </c>
-      <c r="S8" t="n">
-        <v>6</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
       <c r="U8" t="n">
         <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA8" t="n">
         <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AF8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG8" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>h89kUbu5</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>dS1CBple</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>638</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>361</v>
       </c>
       <c r="AM8" t="n">
+        <v>546</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>256</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
         <v>55</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AV8" t="n">
         <v>555</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AW8" t="n">
         <v>0</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AX8" t="n">
         <v>20242025</v>
       </c>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="n">
-        <v>631</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>466</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>562</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>379</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>5</v>
-      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BB8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC8" t="n">
-        <v>25.5</v>
+        <v>24.36363636363636</v>
       </c>
       <c r="BD8" t="n">
-        <v>181</v>
+        <v>180.6363636363636</v>
       </c>
       <c r="BE8" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="BF8" t="inlineStr"/>
+        <v>64.72727272727273</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1818.181818181818</v>
+      </c>
       <c r="BG8" t="n">
-        <v>1235000</v>
+        <v>954545.4545454546</v>
       </c>
       <c r="BH8" t="n">
-        <v>72.2</v>
+        <v>69.63636363636364</v>
       </c>
       <c r="BI8" t="n">
         <v>1</v>
       </c>
       <c r="BJ8" t="n">
-        <v>22.53846153846154</v>
+        <v>26.25</v>
       </c>
       <c r="BK8" t="n">
-        <v>179.0769230769231</v>
+        <v>184.25</v>
       </c>
       <c r="BL8" t="n">
-        <v>63.46153846153846</v>
+        <v>66.75</v>
       </c>
       <c r="BM8" t="inlineStr"/>
       <c r="BN8" t="n">
-        <v>998076.9230769231</v>
+        <v>1118750</v>
       </c>
       <c r="BO8" t="n">
-        <v>71.84615384615384</v>
+        <v>70.25</v>
       </c>
       <c r="BP8" t="n">
         <v>1</v>
       </c>
-      <c r="BQ8" t="inlineStr"/>
-      <c r="BR8" t="inlineStr"/>
-      <c r="BS8" t="inlineStr"/>
-      <c r="BT8" t="inlineStr"/>
-      <c r="BU8" t="inlineStr"/>
-      <c r="BV8" t="inlineStr"/>
-      <c r="BW8" t="inlineStr"/>
-      <c r="BX8" t="inlineStr"/>
+      <c r="BQ8" t="n">
+        <v>23.14285714285714</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>174</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>64.71428571428571</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>2142.857142857143</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1246428.571428571</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>71.85714285714286</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>26.72222222222222</v>
+      </c>
       <c r="BY8" t="n">
+        <v>180.5555555555555</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>65.22222222222223</v>
+      </c>
+      <c r="CA8" t="inlineStr"/>
+      <c r="CB8" t="n">
+        <v>784722.2222222222</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>68.83333333333333</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE8" t="inlineStr"/>
+      <c r="CF8" t="inlineStr"/>
+      <c r="CG8" t="inlineStr"/>
+      <c r="CH8" t="inlineStr"/>
+      <c r="CI8" t="inlineStr"/>
+      <c r="CJ8" t="inlineStr"/>
+      <c r="CK8" t="inlineStr"/>
+      <c r="CL8" t="inlineStr"/>
+      <c r="CM8" t="n">
+        <v>29</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>170</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>66</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>750000</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>66</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8UeBChsf</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45583.625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bouille t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le basser
+  laval </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>11017</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5948</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>31</v>
+      </c>
+      <c r="N9" t="n">
+        <v>69</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>287</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>663</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>191</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>550</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="AU9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="n">
+        <v>33</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="n">
+        <v>26.94736842105263</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>184.4736842105263</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>66</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>2631.578947368421</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1041578.947368421</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>70.89473684210526</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>178</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>61.875</v>
+      </c>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="n">
+        <v>784375</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>131</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>4000</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>925000</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>131</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM9" t="inlineStr"/>
+      <c r="CN9" t="inlineStr"/>
+      <c r="CO9" t="inlineStr"/>
+      <c r="CP9" t="inlineStr"/>
+      <c r="CQ9" t="inlineStr"/>
+      <c r="CR9" t="inlineStr"/>
+      <c r="CS9" t="inlineStr"/>
+      <c r="CT9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>88Kz0Fcl</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45583.625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landry r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis turcan
+  martigues </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>11500</v>
+      </c>
+      <c r="F10" t="n">
+        <v>409</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>59</v>
+      </c>
+      <c r="N10" t="n">
+        <v>41</v>
+      </c>
+      <c r="O10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P10" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>549</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>414</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>452</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>334</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="AU10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>33</v>
+      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
+      <c r="BQ10" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>183</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>840000</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>20.88888888888889</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>62</v>
+      </c>
+      <c r="CA10" t="inlineStr"/>
+      <c r="CB10" t="n">
+        <v>761111.1111111111</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE10" t="inlineStr"/>
+      <c r="CF10" t="inlineStr"/>
+      <c r="CG10" t="inlineStr"/>
+      <c r="CH10" t="inlineStr"/>
+      <c r="CI10" t="inlineStr"/>
+      <c r="CJ10" t="inlineStr"/>
+      <c r="CK10" t="inlineStr"/>
+      <c r="CL10" t="inlineStr"/>
+      <c r="CM10" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>191</v>
+      </c>
+      <c r="CQ10" t="inlineStr"/>
+      <c r="CR10" t="n">
+        <v>2075000</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>204</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>nF72EECs</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45583.625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gaillouste p 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bauer
+  paris   saint ouen </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4643</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>52</v>
+      </c>
+      <c r="N11" t="n">
+        <v>48</v>
+      </c>
+      <c r="O11" t="n">
+        <v>17</v>
+      </c>
+      <c r="P11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>10</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>504</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>410</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>430</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>336</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>18</v>
       </c>
-      <c r="BZ8" t="n">
-        <v>177.5</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>117</v>
-      </c>
-      <c r="CC8" t="inlineStr"/>
-      <c r="CD8" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="CE8" t="n">
-        <v>150</v>
-      </c>
-      <c r="CF8" t="n">
+      <c r="AR11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="AU11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>35</v>
+      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="n">
+        <v>24.77777777777778</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>182.5555555555555</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>67.11111111111111</v>
+      </c>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="n">
+        <v>1430555.555555556</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ11" t="inlineStr"/>
+      <c r="BR11" t="inlineStr"/>
+      <c r="BS11" t="inlineStr"/>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="inlineStr"/>
+      <c r="BW11" t="inlineStr"/>
+      <c r="BX11" t="n">
+        <v>22.08333333333333</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>180</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>64.58333333333333</v>
+      </c>
+      <c r="CA11" t="inlineStr"/>
+      <c r="CB11" t="n">
+        <v>1343750</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>75</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>25</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>182</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>68</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>70</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>26</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>183</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>2</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>131</v>
+      </c>
+      <c r="CQ11" t="inlineStr"/>
+      <c r="CR11" t="n">
+        <v>2050000</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>145</v>
+      </c>
+      <c r="CT11" t="n">
         <v>2</v>
       </c>
     </row>

--- a/data/france/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE2"/>
+  <dimension ref="A1:CL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -660,185 +660,220 @@
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_start_home</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_home</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_home</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_home</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_home</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_away</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_start_away</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_start_away</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_home</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_sub_home</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_away</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_sub_away</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_home</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_home</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_home</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_home</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_home</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_home</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_home</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_home</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_away</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_away</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_away</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_away</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_away</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_away</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_away</t>
         </is>
@@ -847,70 +882,72 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2g2J0IEs</t>
+          <t>f5f1oGre</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45586.65625</v>
+        <v>45587.60416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kubler g 
+          <t xml:space="preserve">gaillouste p 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l aube
-  troyes </t>
+          <t xml:space="preserve">nouste camp
+  pau </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>20420</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>4031</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3431</v>
+      </c>
       <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>39</v>
+      </c>
+      <c r="L2" t="n">
+        <v>61</v>
+      </c>
+      <c r="M2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N2" t="n">
+        <v>10</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>fsfAHubD</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0OEHEprs</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>40</v>
-      </c>
-      <c r="L2" t="n">
-        <v>60</v>
-      </c>
-      <c r="M2" t="n">
-        <v>11</v>
-      </c>
-      <c r="N2" t="n">
-        <v>11</v>
-      </c>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>7</v>
-      </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
@@ -922,10 +959,10 @@
         <v>3</v>
       </c>
       <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4</v>
       </c>
       <c r="Y2" t="n">
         <v>3</v>
@@ -934,55 +971,55 @@
         <v>3</v>
       </c>
       <c r="AA2" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AB2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
-        <v>411</v>
+        <v>361</v>
       </c>
       <c r="AF2" t="n">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="AG2" t="n">
-        <v>347</v>
+        <v>273</v>
       </c>
       <c r="AH2" t="n">
-        <v>604</v>
+        <v>489</v>
       </c>
       <c r="AI2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK2" t="n">
         <v>7</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK2" t="n">
+      <c r="AL2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM2" t="n">
         <v>6</v>
       </c>
-      <c r="AL2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>10</v>
-      </c>
       <c r="AN2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>4vG8dmrf</t>
+          <t>fm0Qb28B</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>zB2j3YvM</t>
+          <t>fo8nHfg4</t>
         </is>
       </c>
       <c r="AQ2" t="n">
@@ -1001,108 +1038,125 @@
         <v>24</v>
       </c>
       <c r="AV2" t="n">
-        <v>179.5</v>
+        <v>186.25</v>
       </c>
       <c r="AW2" t="n">
-        <v>67.375</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3250</v>
-      </c>
+        <v>65.25</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="n">
-        <v>1759375</v>
+        <v>1065625</v>
       </c>
       <c r="AZ2" t="n">
-        <v>71.75</v>
+        <v>71.875</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="BB2" t="n">
-        <v>24.75</v>
+        <v>26.375</v>
       </c>
       <c r="BC2" t="n">
-        <v>176.5</v>
+        <v>178.375</v>
       </c>
       <c r="BD2" t="n">
-        <v>66.125</v>
+        <v>65</v>
       </c>
       <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="n">
-        <v>1285937.5</v>
+        <v>845000</v>
       </c>
       <c r="BG2" t="n">
-        <v>71.5</v>
+        <v>67.875</v>
       </c>
       <c r="BH2" t="n">
         <v>1</v>
       </c>
       <c r="BI2" t="n">
-        <v>28.4375</v>
+        <v>27.0625</v>
       </c>
       <c r="BJ2" t="n">
-        <v>179.9375</v>
+        <v>179.875</v>
       </c>
       <c r="BK2" t="n">
-        <v>67.9375</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>3625</v>
-      </c>
+        <v>65.25</v>
+      </c>
+      <c r="BL2" t="inlineStr"/>
       <c r="BM2" t="n">
-        <v>1217187.5</v>
+        <v>778125</v>
       </c>
       <c r="BN2" t="n">
+        <v>68.3125</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>23.8125</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>179.375</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="n">
+        <v>826562.5</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>68.375</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>170</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>66</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>750000</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>66</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>31</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>180</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH2" t="n">
         <v>69</v>
       </c>
-      <c r="BO2" t="n">
-        <v>1.0625</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>33</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>193</v>
-      </c>
-      <c r="BR2" t="n">
+      <c r="CI2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>69</v>
+      </c>
+      <c r="CL2" t="n">
         <v>1</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>66</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>400000</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>66</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>22.75</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>181.25</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>268</v>
-      </c>
-      <c r="CB2" t="inlineStr"/>
-      <c r="CC2" t="n">
-        <v>5800000</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>287</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL2"/>
+  <dimension ref="A1:CC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,400 +480,355 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>ball_possession_home</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ball_possession_away</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>goal_attempts_home</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>goal_attempts_away</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>shots_on_goal_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>shots_on_goal_away</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>shots_off_goal_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>shots_off_goal_away</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>blocked_shots_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>blocked_shots_away</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>corner_kicks_home</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>corner_kicks_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>offsides_home</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>offsides_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>goalkeeper_saves_home</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>goalkeeper_saves_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>fouls_home</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>fouls_away</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>yellow_cards_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>yellow_cards_away</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>total_passes_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>total_passes_away</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>completed_passes_home</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>completed_passes_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>clearances_completed_home</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>clearances_completed_away</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>crosses_completed_home</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>crosses_completed_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>interceptions_home</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>interceptions_away</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_home</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_home</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_start_home</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_start_home</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_home</t>
-        </is>
-      </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>mean_rep_player_start_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_wage_player_start_away</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_start_away</t>
+          <t>mean_value_player_start_away</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
         <is>
-          <t>mean_value_player_start_away</t>
+          <t>mean_pot_player_start_away</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_away</t>
+          <t>mean_rep_player_start_away</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>mean_rep_player_start_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_sub_home</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_sub_home</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="BK1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_sub_home</t>
+          <t>mean_wage_player_sub_home</t>
         </is>
       </c>
       <c r="BL1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_sub_home</t>
+          <t>mean_value_player_sub_home</t>
         </is>
       </c>
       <c r="BM1" s="1" t="inlineStr">
         <is>
-          <t>mean_value_player_sub_home</t>
+          <t>mean_pot_player_sub_home</t>
         </is>
       </c>
       <c r="BN1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_sub_home</t>
+          <t>mean_rep_player_sub_home</t>
         </is>
       </c>
       <c r="BO1" s="1" t="inlineStr">
         <is>
-          <t>mean_rep_player_sub_home</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="BP1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_sub_away</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="BQ1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_sub_away</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="BR1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_sub_away</t>
+          <t>mean_wage_player_sub_away</t>
         </is>
       </c>
       <c r="BS1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_sub_away</t>
+          <t>mean_value_player_sub_away</t>
         </is>
       </c>
       <c r="BT1" s="1" t="inlineStr">
         <is>
-          <t>mean_value_player_sub_away</t>
+          <t>mean_pot_player_sub_away</t>
         </is>
       </c>
       <c r="BU1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_sub_away</t>
+          <t>mean_rep_player_sub_away</t>
         </is>
       </c>
       <c r="BV1" s="1" t="inlineStr">
         <is>
-          <t>mean_rep_player_sub_away</t>
+          <t>mean_age_player_miss_away</t>
         </is>
       </c>
       <c r="BW1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>mean_hei_player_miss_away</t>
         </is>
       </c>
       <c r="BX1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>n_player_miss_away</t>
         </is>
       </c>
       <c r="BY1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>sum_rat_player_miss_away</t>
         </is>
       </c>
       <c r="BZ1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>sum_wage_player_miss_away</t>
         </is>
       </c>
       <c r="CA1" s="1" t="inlineStr">
         <is>
-          <t>sum_wage_player_miss_home</t>
+          <t>sum_value_player_miss_away</t>
         </is>
       </c>
       <c r="CB1" s="1" t="inlineStr">
         <is>
-          <t>sum_value_player_miss_home</t>
+          <t>sum_pot_player_miss_away</t>
         </is>
       </c>
       <c r="CC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="CD1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="CE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="CF1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="CG1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="CH1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="CI1" s="1" t="inlineStr">
-        <is>
-          <t>sum_wage_player_miss_away</t>
-        </is>
-      </c>
-      <c r="CJ1" s="1" t="inlineStr">
-        <is>
-          <t>sum_value_player_miss_away</t>
-        </is>
-      </c>
-      <c r="CK1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
-      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_away</t>
         </is>
@@ -882,281 +837,1062 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>f5f1oGre</t>
+          <t>AsQgyP6l</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45587.60416666666</v>
+        <v>45592.69791666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">gaillouste p 
+          <t xml:space="preserve">letexier f 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">nouste camp
-  pau </t>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4031</v>
+        <v>67394</v>
       </c>
       <c r="F2" t="n">
-        <v>3431</v>
+        <v>66115</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="M2" t="n">
+        <v>25</v>
+      </c>
+      <c r="N2" t="n">
+        <v>75</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="n">
+      <c r="R2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>9</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W2" t="n">
+        <v>7</v>
+      </c>
+      <c r="X2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6NOhR4cm</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>AZwK8L6R</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>39</v>
-      </c>
-      <c r="L2" t="n">
-        <v>61</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="Z2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="n">
         <v>8</v>
       </c>
-      <c r="N2" t="n">
+      <c r="AC2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>309</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>918</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>241</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>863</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="AW2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>551</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>vNHAXt6D</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F3" t="n">
+        <v>14111</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M3" t="n">
+        <v>52</v>
+      </c>
+      <c r="N3" t="n">
+        <v>48</v>
+      </c>
+      <c r="O3" t="n">
+        <v>9</v>
+      </c>
+      <c r="P3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W3" t="n">
+        <v>20</v>
+      </c>
+      <c r="X3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>487</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>465</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>416</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>403</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT3" t="n">
         <v>10</v>
       </c>
-      <c r="O2" t="n">
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>EgvyJSJo</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="AW3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>551</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr"/>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr"/>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="inlineStr"/>
+      <c r="CC3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F4" t="n">
+        <v>29795</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>40</v>
+      </c>
+      <c r="N4" t="n">
+        <v>60</v>
+      </c>
+      <c r="O4" t="n">
+        <v>17</v>
+      </c>
+      <c r="P4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>9</v>
+      </c>
+      <c r="R4" t="n">
+        <v>5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>11</v>
+      </c>
+      <c r="X4" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE4" t="n">
         <v>4</v>
       </c>
-      <c r="P2" t="n">
+      <c r="AF4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>313</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>477</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>246</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>396</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR4" t="n">
         <v>4</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="AS4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AW4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>551</v>
+      </c>
+      <c r="AY4" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="n">
+      <c r="AZ4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr"/>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F5" t="n">
+        <v>19398</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M5" t="n">
+        <v>50</v>
+      </c>
+      <c r="N5" t="n">
+        <v>50</v>
+      </c>
+      <c r="O5" t="n">
+        <v>9</v>
+      </c>
+      <c r="P5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>17</v>
+      </c>
+      <c r="X5" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z5" t="n">
         <v>4</v>
       </c>
-      <c r="S2" t="n">
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>487</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>479</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>412</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>401</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS5" t="n">
         <v>4</v>
       </c>
-      <c r="T2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="AT5" t="n">
         <v>6</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="AW5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>551</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>3600</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>2725000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="inlineStr"/>
+      <c r="BX5" t="inlineStr"/>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="inlineStr"/>
+      <c r="CA5" t="inlineStr"/>
+      <c r="CB5" t="inlineStr"/>
+      <c r="CC5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WdE2Z2y1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F6" t="n">
+        <v>54868</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>63</v>
+      </c>
+      <c r="N6" t="n">
+        <v>37</v>
+      </c>
+      <c r="O6" t="n">
+        <v>12</v>
+      </c>
+      <c r="P6" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>8</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6</v>
+      </c>
+      <c r="W6" t="n">
+        <v>14</v>
+      </c>
+      <c r="X6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>519</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>286</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>442</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>219</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="AW6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>551</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>182</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="n">
+        <v>1362500</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>71.125</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="n">
+        <v>24.73684210526316</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>180.7894736842105</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>67.10526315789474</v>
+      </c>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="n">
+        <v>1460526.315789474</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>71.52631578947368</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>186</v>
+      </c>
+      <c r="BX6" t="n">
         <v>3</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="BY6" t="n">
+        <v>198</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>219</v>
+      </c>
+      <c r="CC6" t="n">
         <v>3</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>361</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>591</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>273</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>489</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>fm0Qb28B</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>fo8nHfg4</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>555</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>186.25</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>65.25</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="n">
-        <v>1065625</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>71.875</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>26.375</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>178.375</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>65</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="n">
-        <v>845000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>67.875</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>27.0625</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>179.875</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>65.25</v>
-      </c>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="n">
-        <v>778125</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>68.3125</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>23.8125</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>179.375</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>63.25</v>
-      </c>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="n">
-        <v>826562.5</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>68.375</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>29</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>170</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>66</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>750000</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>66</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>31</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>180</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>69</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>3000</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>69</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/france/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC6"/>
+  <dimension ref="A1:CN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,355 +480,410 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>expected_goals_(xg)_home</t>
+          <t>ball_possession_home</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>expected_goals_(xg)_away</t>
+          <t>ball_possession_away</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>ball_possession_home</t>
+          <t>goal_attempts_home</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>ball_possession_away</t>
+          <t>goal_attempts_away</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>goal_attempts_home</t>
+          <t>shots_on_goal_home</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>goal_attempts_away</t>
+          <t>shots_on_goal_away</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>shots_on_goal_home</t>
+          <t>shots_off_goal_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>shots_on_goal_away</t>
+          <t>shots_off_goal_away</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>shots_off_goal_home</t>
+          <t>blocked_shots_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>shots_off_goal_away</t>
+          <t>blocked_shots_away</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>blocked_shots_home</t>
+          <t>corner_kicks_home</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>blocked_shots_away</t>
+          <t>corner_kicks_away</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>free_kicks_home</t>
+          <t>offsides_home</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>free_kicks_away</t>
+          <t>offsides_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>corner_kicks_home</t>
+          <t>goalkeeper_saves_home</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>corner_kicks_away</t>
+          <t>goalkeeper_saves_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>offsides_home</t>
+          <t>fouls_home</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>offsides_away</t>
+          <t>fouls_away</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>throw-ins_home</t>
+          <t>yellow_cards_home</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>throw-ins_away</t>
+          <t>yellow_cards_away</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>goalkeeper_saves_home</t>
+          <t>total_passes_home</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>goalkeeper_saves_away</t>
+          <t>total_passes_away</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>fouls_home</t>
+          <t>completed_passes_home</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>fouls_away</t>
+          <t>completed_passes_away</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
+          <t>clearances_completed_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
           <t>red_cards_home</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>red_cards_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>yellow_cards_home</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>yellow_cards_away</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>total_passes_home</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>total_passes_away</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>completed_passes_home</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>completed_passes_away</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>crosses_completed_home</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>crosses_completed_away</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>interceptions_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>interceptions_away</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>id_country</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>id_competition</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>is_cup</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>mean_wage_player_start_home</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
+          <t>mean_value_player_start_home</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_away</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_start_away</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_start_away</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_home</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_sub_home</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_away</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_sub_away</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_away</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_away</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_away</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_away</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_away</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_away</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_away</t>
         </is>
@@ -837,379 +892,432 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AsQgyP6l</t>
+          <t>K4kBwMoA</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45592.69791666666</v>
+        <v>45594.6875</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
+          <t xml:space="preserve">landry r 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
+          <t xml:space="preserve">stade de la licorne
+  amiens </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>67394</v>
+        <v>12097</v>
       </c>
       <c r="F2" t="n">
-        <v>66115</v>
+        <v>8171</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>31</v>
+      </c>
+      <c r="L2" t="n">
+        <v>69</v>
+      </c>
+      <c r="M2" t="n">
+        <v>15</v>
+      </c>
+      <c r="N2" t="n">
+        <v>14</v>
+      </c>
+      <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="M2" t="n">
-        <v>25</v>
-      </c>
-      <c r="N2" t="n">
-        <v>75</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q2" t="n">
         <v>5</v>
       </c>
-      <c r="P2" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
       <c r="R2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA2" t="n">
         <v>9</v>
       </c>
-      <c r="U2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2</v>
-      </c>
-      <c r="W2" t="n">
-        <v>7</v>
-      </c>
-      <c r="X2" t="n">
+      <c r="AB2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>320</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>686</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>643</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL2" t="n">
         <v>4</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ2" t="n">
+      <c r="AM2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS2" t="n">
         <v>0</v>
       </c>
-      <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>309</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>918</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>241</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>863</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>9</v>
-      </c>
       <c r="AT2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
-        </is>
-      </c>
+        <v>20242025</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="n">
-        <v>55</v>
+        <v>25.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>551</v>
+        <v>178.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
+        <v>66.59999999999999</v>
+      </c>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="n">
+        <v>1195000</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>25.22222222222222</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>177.1111111111111</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>67.55555555555556</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>3333.333333333333</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1722222.222222222</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>71.88888888888889</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>182.9333333333333</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>64</v>
+      </c>
       <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr"/>
-      <c r="BW2" t="inlineStr"/>
-      <c r="BX2" t="inlineStr"/>
+      <c r="BO2" t="n">
+        <v>1036666.666666667</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>26.53846153846154</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>179.3076923076923</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>67.38461538461539</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>3384.615384615385</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1340384.615384615</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>68.92307692307692</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1.076923076923077</v>
+      </c>
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="inlineStr"/>
       <c r="CA2" t="inlineStr"/>
       <c r="CB2" t="inlineStr"/>
       <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
+      <c r="CG2" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>6</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>400</v>
+      </c>
+      <c r="CK2" t="inlineStr"/>
+      <c r="CL2" t="n">
+        <v>7950000</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>425</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vNHAXt6D</t>
+          <t>hImJy0GM</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45592.54166666666</v>
+        <v>45594.6875</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">buquet r 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">stade armand cesari
+  bastia </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>20484</v>
+        <v>16048</v>
       </c>
       <c r="F3" t="n">
-        <v>14111</v>
+        <v>9809</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>62</v>
+      </c>
+      <c r="L3" t="n">
+        <v>38</v>
+      </c>
+      <c r="M3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N3" t="n">
+        <v>14</v>
+      </c>
+      <c r="O3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P3" t="n">
         <v>3</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M3" t="n">
-        <v>52</v>
-      </c>
-      <c r="N3" t="n">
-        <v>48</v>
-      </c>
-      <c r="O3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P3" t="n">
-        <v>15</v>
-      </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V3" t="n">
+        <v>7</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
         <v>4</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AA3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB3" t="n">
         <v>20</v>
       </c>
-      <c r="X3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" t="n">
+      <c r="AC3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>445</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>300</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>356</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>189</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK3" t="n">
         <v>3</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AL3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS3" t="n">
         <v>0</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>487</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>465</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>416</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>403</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>9</v>
-      </c>
       <c r="AT3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>EgvyJSJo</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-      <c r="AW3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>551</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
         <v>20242025</v>
       </c>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
@@ -1220,679 +1328,1833 @@
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
+      <c r="BK3" t="n">
+        <v>24.82352941176471</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>180.0588235294118</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>63.64705882352941</v>
+      </c>
       <c r="BN3" t="inlineStr"/>
-      <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr"/>
+      <c r="BO3" t="n">
+        <v>794117.6470588235</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>67.35294117647059</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>19.83333333333333</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>61.66666666666666</v>
+      </c>
       <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr"/>
-      <c r="BW3" t="inlineStr"/>
-      <c r="BX3" t="inlineStr"/>
-      <c r="BY3" t="inlineStr"/>
-      <c r="BZ3" t="inlineStr"/>
-      <c r="CA3" t="inlineStr"/>
-      <c r="CB3" t="inlineStr"/>
-      <c r="CC3" t="inlineStr"/>
+      <c r="BV3" t="n">
+        <v>775000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>74.33333333333333</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>26</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>172</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>66</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>925000</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>67</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>24</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>185</v>
+      </c>
+      <c r="CK3" t="inlineStr"/>
+      <c r="CL3" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>203</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KdJMr7EE</t>
+          <t>UD9kUH8d</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45592.54166666666</v>
+        <v>45594.6875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pignard j 
+          <t xml:space="preserve">abed k 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
+          <t xml:space="preserve">stade des alpes
+  grenoble </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36178</v>
+        <v>20068</v>
       </c>
       <c r="F4" t="n">
-        <v>29795</v>
+        <v>7920</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>UgPj1p1N</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>25dB6Eto</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1.72</v>
+        <v>49</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4</v>
+        <v>51</v>
       </c>
       <c r="M4" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="N4" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="O4" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>3</v>
+      </c>
+      <c r="W4" t="n">
         <v>5</v>
       </c>
-      <c r="S4" t="n">
-        <v>6</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2</v>
-      </c>
-      <c r="V4" t="n">
-        <v>5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>11</v>
-      </c>
       <c r="X4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>6</v>
       </c>
       <c r="Z4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AA4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AC4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AE4" t="n">
-        <v>4</v>
+        <v>459</v>
       </c>
       <c r="AF4" t="n">
-        <v>7</v>
+        <v>469</v>
       </c>
       <c r="AG4" t="n">
-        <v>16</v>
+        <v>312</v>
       </c>
       <c r="AH4" t="n">
-        <v>11</v>
+        <v>340</v>
       </c>
       <c r="AI4" t="n">
+        <v>41</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS4" t="n">
         <v>0</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>313</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>477</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>246</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>396</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>18</v>
-      </c>
       <c r="AT4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
+        <v>20242025</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>55</v>
+        <v>23.77777777777778</v>
       </c>
       <c r="AX4" t="n">
-        <v>551</v>
+        <v>184.2222222222222</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+        <v>66.11111111111111</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="n">
+        <v>1619444.444444444</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>26.625</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>182.125</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>63.875</v>
+      </c>
       <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr"/>
-      <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
+      <c r="BH4" t="n">
+        <v>615625</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>66.375</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>26.07142857142857</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>184.0714285714286</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>65</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>2785.714285714286</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1083928.571428571</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>68.42857142857143</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>177.3333333333333</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>59.66666666666666</v>
+      </c>
       <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="inlineStr"/>
-      <c r="BW4" t="inlineStr"/>
-      <c r="BX4" t="inlineStr"/>
-      <c r="BY4" t="inlineStr"/>
-      <c r="BZ4" t="inlineStr"/>
-      <c r="CA4" t="inlineStr"/>
-      <c r="CB4" t="inlineStr"/>
-      <c r="CC4" t="inlineStr"/>
+      <c r="BV4" t="n">
+        <v>470833.3333333333</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>68</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>179</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>68</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>400000</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>68</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG4" t="inlineStr"/>
+      <c r="CH4" t="inlineStr"/>
+      <c r="CI4" t="inlineStr"/>
+      <c r="CJ4" t="inlineStr"/>
+      <c r="CK4" t="inlineStr"/>
+      <c r="CL4" t="inlineStr"/>
+      <c r="CM4" t="inlineStr"/>
+      <c r="CN4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h2acepbK</t>
+          <t>Mm6sWwvp</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45592.54166666666</v>
+        <v>45594.6875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ben el hadj salem h 
+          <t xml:space="preserve">valnet a 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
+          <t xml:space="preserve">stade de roudourou
+  guingamp </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>26109</v>
+        <v>19060</v>
       </c>
       <c r="F5" t="n">
-        <v>19398</v>
+        <v>7187</v>
       </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>57</v>
+      </c>
+      <c r="L5" t="n">
+        <v>43</v>
+      </c>
+      <c r="M5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2</v>
+      </c>
+      <c r="W5" t="n">
         <v>3</v>
       </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="M5" t="n">
-        <v>50</v>
-      </c>
-      <c r="N5" t="n">
-        <v>50</v>
-      </c>
-      <c r="O5" t="n">
-        <v>9</v>
-      </c>
-      <c r="P5" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>17</v>
-      </c>
       <c r="X5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z5" t="n">
         <v>4</v>
       </c>
       <c r="AA5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>498</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>418</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>397</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>326</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS5" t="n">
         <v>0</v>
       </c>
-      <c r="AB5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>487</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>479</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>412</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>401</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4</v>
-      </c>
       <c r="AT5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
+        <v>20242025</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>55</v>
+        <v>25.375</v>
       </c>
       <c r="AX5" t="n">
-        <v>551</v>
+        <v>179.875</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>66.125</v>
       </c>
       <c r="AZ5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+        <v>2250</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1103125</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>69.875</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>180.125</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>66.75</v>
+      </c>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="n">
-        <v>22.6</v>
+        <v>937500</v>
       </c>
       <c r="BI5" t="n">
-        <v>183.8</v>
+        <v>70.5</v>
       </c>
       <c r="BJ5" t="n">
-        <v>69.2</v>
+        <v>1</v>
       </c>
       <c r="BK5" t="n">
-        <v>3600</v>
+        <v>24.05882352941176</v>
       </c>
       <c r="BL5" t="n">
-        <v>2725000</v>
+        <v>179.2352941176471</v>
       </c>
       <c r="BM5" t="n">
-        <v>77.59999999999999</v>
+        <v>63.88235294117647</v>
       </c>
       <c r="BN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
-      <c r="BQ5" t="inlineStr"/>
-      <c r="BR5" t="inlineStr"/>
-      <c r="BS5" t="inlineStr"/>
-      <c r="BT5" t="inlineStr"/>
+        <v>1647.058823529412</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>888235.2941176471</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>69.29411764705883</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>179.5333333333333</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>63.06666666666667</v>
+      </c>
       <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="inlineStr"/>
-      <c r="BW5" t="inlineStr"/>
-      <c r="BX5" t="inlineStr"/>
+      <c r="BV5" t="n">
+        <v>840000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>69.13333333333334</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1</v>
+      </c>
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="inlineStr"/>
       <c r="CA5" t="inlineStr"/>
       <c r="CB5" t="inlineStr"/>
       <c r="CC5" t="inlineStr"/>
+      <c r="CD5" t="inlineStr"/>
+      <c r="CE5" t="inlineStr"/>
+      <c r="CF5" t="inlineStr"/>
+      <c r="CG5" t="n">
+        <v>36</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>179</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>67</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>350000</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>67</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WdE2Z2y1</t>
+          <t>CYrglw0S</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45592.45833333334</v>
+        <v>45594.6875</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">kubler g 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
+          <t xml:space="preserve">stade francis le basser
+  laval </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>59186</v>
+        <v>11017</v>
       </c>
       <c r="F6" t="n">
-        <v>54868</v>
+        <v>6799</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>E1wDrLsJ</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>IRuMRua1</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1.87</v>
+        <v>45</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>55</v>
       </c>
       <c r="M6" t="n">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="N6" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>449</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>547</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>360</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>471</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK6" t="n">
         <v>8</v>
       </c>
-      <c r="R6" t="n">
-        <v>4</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2</v>
-      </c>
-      <c r="V6" t="n">
+      <c r="AL6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN6" t="n">
         <v>6</v>
       </c>
-      <c r="W6" t="n">
-        <v>14</v>
-      </c>
-      <c r="X6" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="n">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>E3v5aJXp</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS6" t="n">
         <v>0</v>
       </c>
-      <c r="AL6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>519</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>286</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>442</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>219</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>7</v>
-      </c>
       <c r="AT6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-      <c r="AW6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>551</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
         <v>20242025</v>
       </c>
-      <c r="BA6" t="n">
-        <v>25.125</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>182</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>66.625</v>
-      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="n">
-        <v>1362500</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>71.125</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>1</v>
-      </c>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr"/>
       <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
+      <c r="BK6" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>63.93333333333333</v>
+      </c>
       <c r="BN6" t="inlineStr"/>
       <c r="BO6" t="n">
-        <v>24.73684210526316</v>
+        <v>1027666.666666667</v>
       </c>
       <c r="BP6" t="n">
-        <v>180.7894736842105</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="BQ6" t="n">
-        <v>67.10526315789474</v>
-      </c>
-      <c r="BR6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>24.71428571428572</v>
+      </c>
       <c r="BS6" t="n">
-        <v>1460526.315789474</v>
+        <v>177.5714285714286</v>
       </c>
       <c r="BT6" t="n">
-        <v>71.52631578947368</v>
+        <v>63.42857142857143</v>
       </c>
       <c r="BU6" t="n">
-        <v>1</v>
+        <v>2285.714285714286</v>
       </c>
       <c r="BV6" t="n">
+        <v>939285.7142857143</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>68.14285714285714</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>30</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>3</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>197</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>2025000</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>202</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>3</v>
+      </c>
+      <c r="CG6" t="inlineStr"/>
+      <c r="CH6" t="inlineStr"/>
+      <c r="CI6" t="inlineStr"/>
+      <c r="CJ6" t="inlineStr"/>
+      <c r="CK6" t="inlineStr"/>
+      <c r="CL6" t="inlineStr"/>
+      <c r="CM6" t="inlineStr"/>
+      <c r="CN6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>A9nxhL03</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45594.6875</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gaillouste p 
+  fra </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade du moustoir
+  lorient </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>16787</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12036</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>47</v>
+      </c>
+      <c r="L7" t="n">
+        <v>53</v>
+      </c>
+      <c r="M7" t="n">
+        <v>11</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>9</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>396</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>473</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>308</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>378</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+      <c r="BO7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr"/>
+      <c r="BQ7" t="inlineStr"/>
+      <c r="BR7" t="n">
+        <v>25.91666666666667</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>177.4166666666667</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="n">
+        <v>741666.6666666666</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>70.58333333333333</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY7" t="n">
         <v>24</v>
       </c>
-      <c r="BW6" t="n">
+      <c r="BZ7" t="n">
+        <v>173</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>71</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>13000</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>74</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG7" t="inlineStr"/>
+      <c r="CH7" t="inlineStr"/>
+      <c r="CI7" t="inlineStr"/>
+      <c r="CJ7" t="inlineStr"/>
+      <c r="CK7" t="inlineStr"/>
+      <c r="CL7" t="inlineStr"/>
+      <c r="CM7" t="inlineStr"/>
+      <c r="CN7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Oxd2urHc</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45594.6875</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rosier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis turcan
+  martigues </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>11500</v>
+      </c>
+      <c r="F8" t="n">
+        <v>580</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>42</v>
+      </c>
+      <c r="L8" t="n">
+        <v>58</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" t="n">
+        <v>15</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>7</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>359</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>479</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>270</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>393</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>65.625</v>
+      </c>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="n">
+        <v>1543750</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>26.42857142857143</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>183.2857142857143</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>65.14285714285714</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>850000</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>66.85714285714286</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="BS8" t="n">
         <v>186</v>
       </c>
-      <c r="BX6" t="n">
+      <c r="BT8" t="n">
+        <v>66.72727272727273</v>
+      </c>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="n">
+        <v>1115909.090909091</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>70.81818181818181</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
+      <c r="CA8" t="inlineStr"/>
+      <c r="CB8" t="inlineStr"/>
+      <c r="CC8" t="inlineStr"/>
+      <c r="CD8" t="inlineStr"/>
+      <c r="CE8" t="inlineStr"/>
+      <c r="CF8" t="inlineStr"/>
+      <c r="CG8" t="inlineStr"/>
+      <c r="CH8" t="inlineStr"/>
+      <c r="CI8" t="inlineStr"/>
+      <c r="CJ8" t="inlineStr"/>
+      <c r="CK8" t="inlineStr"/>
+      <c r="CL8" t="inlineStr"/>
+      <c r="CM8" t="inlineStr"/>
+      <c r="CN8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>IZkpjaVF</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45594.6875</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapapria r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bauer
+  paris   saint ouen </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4643</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>36</v>
+      </c>
+      <c r="L9" t="n">
+        <v>64</v>
+      </c>
+      <c r="M9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N9" t="n">
+        <v>16</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>9</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>13</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
         <v>3</v>
       </c>
-      <c r="BY6" t="n">
-        <v>198</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>9000</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>5300000</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>219</v>
-      </c>
-      <c r="CC6" t="n">
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>373</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>642</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>301</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>579</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>43</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr"/>
+      <c r="CE9" t="inlineStr"/>
+      <c r="CF9" t="inlineStr"/>
+      <c r="CG9" t="inlineStr"/>
+      <c r="CH9" t="inlineStr"/>
+      <c r="CI9" t="inlineStr"/>
+      <c r="CJ9" t="inlineStr"/>
+      <c r="CK9" t="inlineStr"/>
+      <c r="CL9" t="inlineStr"/>
+      <c r="CM9" t="inlineStr"/>
+      <c r="CN9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>U5gzczE6</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45594.6875</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bouille t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l aube
+  troyes </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>20420</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4810</v>
+      </c>
+      <c r="G10" t="n">
         <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>38</v>
+      </c>
+      <c r="L10" t="n">
+        <v>62</v>
+      </c>
+      <c r="M10" t="n">
+        <v>18</v>
+      </c>
+      <c r="N10" t="n">
+        <v>9</v>
+      </c>
+      <c r="O10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>409</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>673</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>337</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>585</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>33</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>66</v>
+      </c>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="n">
+        <v>1206250</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>71.625</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>64.88888888888889</v>
+      </c>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="n">
+        <v>1069444.444444444</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>71.44444444444444</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>24.06666666666667</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>174.9333333333333</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>64.86666666666666</v>
+      </c>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="n">
+        <v>1116666.666666667</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>70.73333333333333</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>29.06666666666667</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>180.0666666666667</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>66.53333333333333</v>
+      </c>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="n">
+        <v>796666.6666666666</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>28</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>5</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>340</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>19000</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>356</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>6</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>29</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>170</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>66</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>750000</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>66</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
